--- a/master_activity.xlsx
+++ b/master_activity.xlsx
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -862,10 +862,157 @@
         <v>177</v>
       </c>
     </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>06/01/2026 - 06/07/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="8" t="inlineStr"/>
+      <c r="H7" s="8" t="inlineStr"/>
+      <c r="I7" s="8" t="inlineStr"/>
+      <c r="J7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" s="8" t="inlineStr"/>
+      <c r="L7" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="M7" s="8" t="inlineStr"/>
+      <c r="N7" s="8" t="inlineStr"/>
+      <c r="O7" s="8" t="inlineStr"/>
+      <c r="P7" s="8" t="inlineStr"/>
+      <c r="Q7" s="8" t="inlineStr"/>
+      <c r="R7" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>06/01/2026 - 06/07/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="inlineStr"/>
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr"/>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>06/01/2026 - 06/07/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>JR Scappini</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8" t="inlineStr"/>
+      <c r="E9" s="8" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr"/>
+      <c r="G9" s="8" t="inlineStr"/>
+      <c r="H9" s="8" t="inlineStr"/>
+      <c r="I9" s="8" t="inlineStr"/>
+      <c r="J9" s="8" t="inlineStr"/>
+      <c r="K9" s="8" t="inlineStr"/>
+      <c r="L9" s="8" t="inlineStr"/>
+      <c r="M9" s="8" t="inlineStr"/>
+      <c r="N9" s="8" t="inlineStr"/>
+      <c r="O9" s="8" t="inlineStr"/>
+      <c r="P9" s="8" t="inlineStr"/>
+      <c r="Q9" s="8" t="inlineStr"/>
+      <c r="R9" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 06/01/2026 - 06/07/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+      <c r="R10" s="5" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:R1"/>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -877,7 +1024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1218,9 +1365,156 @@
         <v>177</v>
       </c>
     </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>06/01/2026 - 06/07/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="8" t="inlineStr"/>
+      <c r="H7" s="8" t="inlineStr"/>
+      <c r="I7" s="8" t="inlineStr"/>
+      <c r="J7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" s="8" t="inlineStr"/>
+      <c r="L7" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="M7" s="8" t="inlineStr"/>
+      <c r="N7" s="8" t="inlineStr"/>
+      <c r="O7" s="8" t="inlineStr"/>
+      <c r="P7" s="8" t="inlineStr"/>
+      <c r="Q7" s="8" t="inlineStr"/>
+      <c r="R7" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>06/01/2026 - 06/07/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="inlineStr"/>
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr"/>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>06/01/2026 - 06/07/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>JR Scappini</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8" t="inlineStr"/>
+      <c r="E9" s="8" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr"/>
+      <c r="G9" s="8" t="inlineStr"/>
+      <c r="H9" s="8" t="inlineStr"/>
+      <c r="I9" s="8" t="inlineStr"/>
+      <c r="J9" s="8" t="inlineStr"/>
+      <c r="K9" s="8" t="inlineStr"/>
+      <c r="L9" s="8" t="inlineStr"/>
+      <c r="M9" s="8" t="inlineStr"/>
+      <c r="N9" s="8" t="inlineStr"/>
+      <c r="O9" s="8" t="inlineStr"/>
+      <c r="P9" s="8" t="inlineStr"/>
+      <c r="Q9" s="8" t="inlineStr"/>
+      <c r="R9" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 06/01/2026 - 06/07/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+      <c r="R10" s="5" t="n">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_activity.xlsx
+++ b/master_activity.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet name="All Weeks" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Wk 05-25-2026" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Wk 06-01-2026" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Weeks'!$A$1:$R$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Weeks'!$A$1:$P$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -521,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -557,59 +558,59 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Activity/General Notes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Appointment - Completed</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Appointment - Scheduled</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Cold Call Via Email</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Cold Call Visit - Successful</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Cold Call Visit - Unsuccessful</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Cold Call via Phone</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Courtesy Phone Call</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Courtesy Site Visit</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Group Email</t>
-        </is>
-      </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Payment Delivery</t>
@@ -617,7 +618,7 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Phone - Incoming</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
@@ -873,35 +874,43 @@
           <t>Carlos Casillas</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n">
-        <v>1</v>
-      </c>
+      <c r="C7" s="8" t="inlineStr"/>
       <c r="D7" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" s="8" t="inlineStr"/>
-      <c r="H7" s="8" t="inlineStr"/>
-      <c r="I7" s="8" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>9</v>
+      </c>
       <c r="J7" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" s="8" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>47</v>
+      </c>
       <c r="L7" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>68</v>
+      </c>
+      <c r="N7" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="M7" s="8" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr"/>
       <c r="O7" s="8" t="inlineStr"/>
-      <c r="P7" s="8" t="inlineStr"/>
-      <c r="Q7" s="8" t="inlineStr"/>
-      <c r="R7" s="5" t="n">
-        <v>21</v>
+      <c r="P7" s="5" t="n">
+        <v>221</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -915,25 +924,39 @@
           <t>Christine Mello</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>7</v>
+      </c>
       <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="G8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="4" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>13</v>
+      </c>
       <c r="J8" s="4" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr"/>
-      <c r="O8" s="4" t="inlineStr"/>
-      <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="4" t="inlineStr"/>
-      <c r="R8" s="5" t="n">
-        <v>2</v>
+      <c r="N8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="5" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -944,12 +967,10 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>JR Scappini</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>1</v>
-      </c>
+          <t>Harrison Shr</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr"/>
       <c r="D9" s="8" t="inlineStr"/>
       <c r="E9" s="8" t="inlineStr"/>
       <c r="F9" s="8" t="inlineStr"/>
@@ -960,59 +981,138 @@
       <c r="K9" s="8" t="inlineStr"/>
       <c r="L9" s="8" t="inlineStr"/>
       <c r="M9" s="8" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="O9" s="8" t="inlineStr"/>
-      <c r="P9" s="8" t="inlineStr"/>
-      <c r="Q9" s="8" t="inlineStr"/>
-      <c r="R9" s="5" t="n">
+      <c r="P9" s="5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>06/01/2026 - 06/07/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>JR Scappini</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr"/>
+      <c r="L10" s="4" t="inlineStr"/>
+      <c r="M10" s="4" t="inlineStr"/>
+      <c r="N10" s="4" t="inlineStr"/>
+      <c r="O10" s="4" t="inlineStr"/>
+      <c r="P10" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>06/01/2026 - 06/07/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr"/>
+      <c r="D11" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" s="8" t="inlineStr"/>
+      <c r="F11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="8" t="inlineStr"/>
+      <c r="H11" s="8" t="inlineStr"/>
+      <c r="I11" s="8" t="inlineStr"/>
+      <c r="J11" s="8" t="inlineStr"/>
+      <c r="K11" s="8" t="inlineStr"/>
+      <c r="L11" s="8" t="inlineStr"/>
+      <c r="M11" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" s="8" t="inlineStr"/>
+      <c r="O11" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>WEEK TOTAL — 06/01/2026 - 06/07/2026</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="5" t="n">
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="O12" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="G10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" s="5" t="inlineStr"/>
-      <c r="L10" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="M10" s="5" t="inlineStr"/>
-      <c r="N10" s="5" t="inlineStr"/>
-      <c r="O10" s="5" t="inlineStr"/>
-      <c r="P10" s="5" t="inlineStr"/>
-      <c r="Q10" s="5" t="inlineStr"/>
-      <c r="R10" s="5" t="n">
-        <v>24</v>
+      <c r="P12" s="5" t="n">
+        <v>335</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R1"/>
-  <mergeCells count="2">
+  <autoFilter ref="A1:P1"/>
+  <mergeCells count="3">
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1518,4 +1618,365 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Activity/General Notes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Completed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Scheduled</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Via Email</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Successful</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Unsuccessful</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call via Phone</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Phone Call</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Site Visit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Payment Delivery</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>06/01/2026 - 06/07/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="O2" s="4" t="inlineStr"/>
+      <c r="P2" s="5" t="n">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>06/01/2026 - 06/07/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" s="5" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>06/01/2026 - 06/07/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Harrison Shr</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>06/01/2026 - 06/07/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>JR Scappini</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="8" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>06/01/2026 - 06/07/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" s="4" t="inlineStr"/>
+      <c r="O6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 06/01/2026 - 06/07/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>335</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A7:B7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/master_activity.xlsx
+++ b/master_activity.xlsx
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -916,9 +916,140 @@
         <v>335</v>
       </c>
     </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>06/08/2026 - 06/14/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr"/>
+      <c r="T8" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>06/08/2026 - 06/14/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr"/>
+      <c r="D9" s="8" t="inlineStr"/>
+      <c r="E9" s="8" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr"/>
+      <c r="G9" s="8" t="inlineStr"/>
+      <c r="H9" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" s="8" t="inlineStr"/>
+      <c r="K9" s="8" t="inlineStr"/>
+      <c r="L9" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N9" s="8" t="inlineStr"/>
+      <c r="O9" s="8" t="inlineStr"/>
+      <c r="P9" s="8" t="inlineStr"/>
+      <c r="Q9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" s="8" t="inlineStr"/>
+      <c r="S9" s="8" t="inlineStr"/>
+      <c r="T9" s="5" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 06/08/2026 - 06/14/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" s="5" t="inlineStr"/>
+      <c r="S10" s="5" t="inlineStr"/>
+      <c r="T10" s="5" t="n">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A10:B10"/>
     <mergeCell ref="A7:B7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -931,7 +1062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1326,8 +1457,139 @@
         <v>335</v>
       </c>
     </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>06/08/2026 - 06/14/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr"/>
+      <c r="T8" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>06/08/2026 - 06/14/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr"/>
+      <c r="D9" s="8" t="inlineStr"/>
+      <c r="E9" s="8" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr"/>
+      <c r="G9" s="8" t="inlineStr"/>
+      <c r="H9" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" s="8" t="inlineStr"/>
+      <c r="K9" s="8" t="inlineStr"/>
+      <c r="L9" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N9" s="8" t="inlineStr"/>
+      <c r="O9" s="8" t="inlineStr"/>
+      <c r="P9" s="8" t="inlineStr"/>
+      <c r="Q9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" s="8" t="inlineStr"/>
+      <c r="S9" s="8" t="inlineStr"/>
+      <c r="T9" s="5" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 06/08/2026 - 06/14/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" s="5" t="inlineStr"/>
+      <c r="S10" s="5" t="inlineStr"/>
+      <c r="T10" s="5" t="n">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A10:B10"/>
     <mergeCell ref="A7:B7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/master_activity.xlsx
+++ b/master_activity.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="All Weeks" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Wk 06-01-2026" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Wk 06-08-2026" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Weeks'!$A$1:$T$1</definedName>
@@ -521,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:T15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -930,32 +931,42 @@
       <c r="C8" s="4" t="inlineStr"/>
       <c r="D8" s="4" t="inlineStr"/>
       <c r="E8" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="4" t="inlineStr"/>
-      <c r="J8" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>20</v>
+      </c>
       <c r="K8" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="L8" s="4" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="M8" s="4" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="N8" s="4" t="inlineStr"/>
       <c r="O8" s="4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="P8" s="4" t="inlineStr"/>
       <c r="Q8" s="4" t="inlineStr"/>
       <c r="R8" s="4" t="inlineStr"/>
       <c r="S8" s="4" t="inlineStr"/>
       <c r="T8" s="5" t="n">
-        <v>30</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -970,85 +981,293 @@
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr"/>
-      <c r="D9" s="8" t="inlineStr"/>
+      <c r="D9" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="E9" s="8" t="inlineStr"/>
       <c r="F9" s="8" t="inlineStr"/>
-      <c r="G9" s="8" t="inlineStr"/>
+      <c r="G9" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="H9" s="8" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="J9" s="8" t="inlineStr"/>
       <c r="K9" s="8" t="inlineStr"/>
       <c r="L9" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N9" s="8" t="inlineStr"/>
-      <c r="O9" s="8" t="inlineStr"/>
+      <c r="O9" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="P9" s="8" t="inlineStr"/>
       <c r="Q9" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" s="8" t="inlineStr"/>
-      <c r="S9" s="8" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="R9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="T9" s="5" t="n">
-        <v>14</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>06/08/2026 - 06/14/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr"/>
+      <c r="L10" s="4" t="inlineStr"/>
+      <c r="M10" s="4" t="inlineStr"/>
+      <c r="N10" s="4" t="n">
+        <v>148</v>
+      </c>
+      <c r="O10" s="4" t="inlineStr"/>
+      <c r="P10" s="4" t="inlineStr"/>
+      <c r="Q10" s="4" t="inlineStr"/>
+      <c r="R10" s="4" t="inlineStr"/>
+      <c r="S10" s="4" t="inlineStr"/>
+      <c r="T10" s="5" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>06/08/2026 - 06/14/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr"/>
+      <c r="D11" s="8" t="inlineStr"/>
+      <c r="E11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" s="8" t="inlineStr"/>
+      <c r="K11" s="8" t="inlineStr"/>
+      <c r="L11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="8" t="inlineStr"/>
+      <c r="N11" s="8" t="inlineStr"/>
+      <c r="O11" s="8" t="inlineStr"/>
+      <c r="P11" s="8" t="inlineStr"/>
+      <c r="Q11" s="8" t="inlineStr"/>
+      <c r="R11" s="8" t="inlineStr"/>
+      <c r="S11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>WEEK TOTAL — 06/08/2026 - 06/14/2026</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" s="5" t="n">
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>148</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="N10" s="5" t="inlineStr"/>
-      <c r="O10" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="P10" s="5" t="inlineStr"/>
-      <c r="Q10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" s="5" t="inlineStr"/>
-      <c r="S10" s="5" t="inlineStr"/>
-      <c r="T10" s="5" t="n">
-        <v>44</v>
+      <c r="T12" s="5" t="n">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>06/15/2026 - 06/21/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr"/>
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="8" t="inlineStr"/>
+      <c r="F13" s="8" t="inlineStr"/>
+      <c r="G13" s="8" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr"/>
+      <c r="I13" s="8" t="inlineStr"/>
+      <c r="J13" s="8" t="inlineStr"/>
+      <c r="K13" s="8" t="inlineStr"/>
+      <c r="L13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="8" t="inlineStr"/>
+      <c r="N13" s="8" t="inlineStr"/>
+      <c r="O13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" s="8" t="inlineStr"/>
+      <c r="Q13" s="8" t="inlineStr"/>
+      <c r="R13" s="8" t="inlineStr"/>
+      <c r="S13" s="8" t="inlineStr"/>
+      <c r="T13" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>06/15/2026 - 06/21/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" s="4" t="inlineStr"/>
+      <c r="J14" s="4" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr"/>
+      <c r="L14" s="4" t="inlineStr"/>
+      <c r="M14" s="4" t="inlineStr"/>
+      <c r="N14" s="4" t="inlineStr"/>
+      <c r="O14" s="4" t="inlineStr"/>
+      <c r="P14" s="4" t="inlineStr"/>
+      <c r="Q14" s="4" t="inlineStr"/>
+      <c r="R14" s="4" t="inlineStr"/>
+      <c r="S14" s="4" t="inlineStr"/>
+      <c r="T14" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 06/15/2026 - 06/21/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr"/>
+      <c r="R15" s="5" t="inlineStr"/>
+      <c r="S15" s="5" t="inlineStr"/>
+      <c r="T15" s="5" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <mergeCells count="2">
+  <mergeCells count="4">
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A12:B12"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A7:B7"/>
   </mergeCells>
@@ -1594,4 +1813,492 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Activity/General Notes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Completed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Scheduled</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Via Email</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Successful</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Unsuccessful</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call via Phone</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Phone Call</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Site Visit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Group Email</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Payment Delivery</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Incoming</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Outgoing</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>06/08/2026 - 06/14/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="N2" s="4" t="inlineStr"/>
+      <c r="O2" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="P2" s="4" t="inlineStr"/>
+      <c r="Q2" s="4" t="inlineStr"/>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
+      <c r="T2" s="5" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>06/08/2026 - 06/14/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" s="8" t="inlineStr"/>
+      <c r="Q3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" s="5" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>06/08/2026 - 06/14/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="n">
+        <v>148</v>
+      </c>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="5" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>06/08/2026 - 06/14/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr"/>
+      <c r="E5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 06/08/2026 - 06/14/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>148</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>06/15/2026 - 06/21/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr"/>
+      <c r="D7" s="8" t="inlineStr"/>
+      <c r="E7" s="8" t="inlineStr"/>
+      <c r="F7" s="8" t="inlineStr"/>
+      <c r="G7" s="8" t="inlineStr"/>
+      <c r="H7" s="8" t="inlineStr"/>
+      <c r="I7" s="8" t="inlineStr"/>
+      <c r="J7" s="8" t="inlineStr"/>
+      <c r="K7" s="8" t="inlineStr"/>
+      <c r="L7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="8" t="inlineStr"/>
+      <c r="N7" s="8" t="inlineStr"/>
+      <c r="O7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" s="8" t="inlineStr"/>
+      <c r="Q7" s="8" t="inlineStr"/>
+      <c r="R7" s="8" t="inlineStr"/>
+      <c r="S7" s="8" t="inlineStr"/>
+      <c r="T7" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>06/15/2026 - 06/21/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="inlineStr"/>
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr"/>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr"/>
+      <c r="T8" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 06/15/2026 - 06/21/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr"/>
+      <c r="S9" s="5" t="inlineStr"/>
+      <c r="T9" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A6:B6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/master_activity.xlsx
+++ b/master_activity.xlsx
@@ -10,6 +10,7 @@
     <sheet name="All Weeks" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Wk 06-01-2026" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Wk 06-08-2026" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Wk 06-15-2026" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Weeks'!$A$1:$T$1</definedName>
@@ -522,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T15"/>
+  <dimension ref="A1:T22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1027,11 +1028,7 @@
           <t>06/08/2026 - 06/14/2026</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Michael Petrick</t>
-        </is>
-      </c>
+      <c r="B10" s="10" t="n"/>
       <c r="C10" s="4" t="inlineStr"/>
       <c r="D10" s="4" t="inlineStr"/>
       <c r="E10" s="4" t="inlineStr"/>
@@ -1167,32 +1164,50 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Michael Petrick</t>
+          <t>Carlos Casillas</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr"/>
       <c r="D13" s="8" t="inlineStr"/>
-      <c r="E13" s="8" t="inlineStr"/>
-      <c r="F13" s="8" t="inlineStr"/>
-      <c r="G13" s="8" t="inlineStr"/>
-      <c r="H13" s="8" t="inlineStr"/>
-      <c r="I13" s="8" t="inlineStr"/>
-      <c r="J13" s="8" t="inlineStr"/>
-      <c r="K13" s="8" t="inlineStr"/>
+      <c r="E13" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J13" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K13" s="8" t="n">
+        <v>46</v>
+      </c>
       <c r="L13" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" s="8" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="M13" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="N13" s="8" t="n">
+        <v>215</v>
+      </c>
       <c r="O13" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P13" s="8" t="inlineStr"/>
       <c r="Q13" s="8" t="inlineStr"/>
       <c r="R13" s="8" t="inlineStr"/>
       <c r="S13" s="8" t="inlineStr"/>
       <c r="T13" s="5" t="n">
-        <v>2</v>
+        <v>385</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
@@ -1203,73 +1218,387 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Roger Guzowski</t>
+          <t>Christine Mello</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
       <c r="D14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr"/>
-      <c r="I14" s="4" t="inlineStr"/>
-      <c r="J14" s="4" t="inlineStr"/>
-      <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4" t="inlineStr"/>
-      <c r="M14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>9</v>
+      </c>
       <c r="N14" s="4" t="inlineStr"/>
-      <c r="O14" s="4" t="inlineStr"/>
-      <c r="P14" s="4" t="inlineStr"/>
-      <c r="Q14" s="4" t="inlineStr"/>
-      <c r="R14" s="4" t="inlineStr"/>
+      <c r="O14" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="P14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="S14" s="4" t="inlineStr"/>
       <c r="T14" s="5" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>06/15/2026 - 06/21/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>JR Scappini</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr"/>
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="8" t="inlineStr"/>
+      <c r="G15" s="8" t="inlineStr"/>
+      <c r="H15" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="I15" s="8" t="inlineStr"/>
+      <c r="J15" s="8" t="inlineStr"/>
+      <c r="K15" s="8" t="inlineStr"/>
+      <c r="L15" s="8" t="inlineStr"/>
+      <c r="M15" s="8" t="inlineStr"/>
+      <c r="N15" s="8" t="inlineStr"/>
+      <c r="O15" s="8" t="inlineStr"/>
+      <c r="P15" s="8" t="inlineStr"/>
+      <c r="Q15" s="8" t="inlineStr"/>
+      <c r="R15" s="8" t="inlineStr"/>
+      <c r="S15" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" s="5" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>06/15/2026 - 06/21/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr"/>
+      <c r="J16" s="4" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr"/>
+      <c r="L16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="4" t="inlineStr"/>
+      <c r="N16" s="4" t="inlineStr"/>
+      <c r="O16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" s="4" t="inlineStr"/>
+      <c r="Q16" s="4" t="inlineStr"/>
+      <c r="R16" s="4" t="inlineStr"/>
+      <c r="S16" s="4" t="inlineStr"/>
+      <c r="T16" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>06/15/2026 - 06/21/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr"/>
+      <c r="D17" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E17" s="8" t="inlineStr"/>
+      <c r="F17" s="8" t="inlineStr"/>
+      <c r="G17" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="8" t="inlineStr"/>
+      <c r="I17" s="8" t="inlineStr"/>
+      <c r="J17" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K17" s="8" t="inlineStr"/>
+      <c r="L17" s="8" t="inlineStr"/>
+      <c r="M17" s="8" t="inlineStr"/>
+      <c r="N17" s="8" t="inlineStr"/>
+      <c r="O17" s="8" t="inlineStr"/>
+      <c r="P17" s="8" t="inlineStr"/>
+      <c r="Q17" s="8" t="inlineStr"/>
+      <c r="R17" s="8" t="inlineStr"/>
+      <c r="S17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>WEEK TOTAL — 06/15/2026 - 06/21/2026</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="5" t="inlineStr"/>
-      <c r="D15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr"/>
-      <c r="G15" s="5" t="inlineStr"/>
-      <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="5" t="inlineStr"/>
-      <c r="K15" s="5" t="inlineStr"/>
-      <c r="L15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" s="5" t="inlineStr"/>
-      <c r="N15" s="5" t="inlineStr"/>
-      <c r="O15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" s="5" t="inlineStr"/>
-      <c r="Q15" s="5" t="inlineStr"/>
-      <c r="R15" s="5" t="inlineStr"/>
-      <c r="S15" s="5" t="inlineStr"/>
-      <c r="T15" s="5" t="n">
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" s="5" t="n">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>06/22/2026 - 06/28/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr"/>
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="8" t="inlineStr"/>
+      <c r="F19" s="8" t="inlineStr"/>
+      <c r="G19" s="8" t="inlineStr"/>
+      <c r="H19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="8" t="n">
         <v>3</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" s="8" t="inlineStr"/>
+      <c r="L19" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="8" t="inlineStr"/>
+      <c r="N19" s="8" t="inlineStr"/>
+      <c r="O19" s="8" t="inlineStr"/>
+      <c r="P19" s="8" t="inlineStr"/>
+      <c r="Q19" s="8" t="inlineStr"/>
+      <c r="R19" s="8" t="inlineStr"/>
+      <c r="S19" s="8" t="inlineStr"/>
+      <c r="T19" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>06/22/2026 - 06/28/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr"/>
+      <c r="D20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr"/>
+      <c r="J20" s="4" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr"/>
+      <c r="L20" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" s="4" t="inlineStr"/>
+      <c r="N20" s="4" t="inlineStr"/>
+      <c r="O20" s="4" t="inlineStr"/>
+      <c r="P20" s="4" t="inlineStr"/>
+      <c r="Q20" s="4" t="inlineStr"/>
+      <c r="R20" s="4" t="inlineStr"/>
+      <c r="S20" s="4" t="inlineStr"/>
+      <c r="T20" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>06/22/2026 - 06/28/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr"/>
+      <c r="D21" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="8" t="inlineStr"/>
+      <c r="F21" s="8" t="inlineStr"/>
+      <c r="G21" s="8" t="inlineStr"/>
+      <c r="H21" s="8" t="inlineStr"/>
+      <c r="I21" s="8" t="inlineStr"/>
+      <c r="J21" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" s="8" t="inlineStr"/>
+      <c r="L21" s="8" t="inlineStr"/>
+      <c r="M21" s="8" t="inlineStr"/>
+      <c r="N21" s="8" t="inlineStr"/>
+      <c r="O21" s="8" t="inlineStr"/>
+      <c r="P21" s="8" t="inlineStr"/>
+      <c r="Q21" s="8" t="inlineStr"/>
+      <c r="R21" s="8" t="inlineStr"/>
+      <c r="S21" s="8" t="inlineStr"/>
+      <c r="T21" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 06/22/2026 - 06/28/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr"/>
+      <c r="R22" s="5" t="inlineStr"/>
+      <c r="S22" s="5" t="inlineStr"/>
+      <c r="T22" s="5" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <mergeCells count="4">
+  <mergeCells count="6">
     <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A22:B22"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A7:B7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2301,4 +2630,580 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Activity/General Notes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Completed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Scheduled</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Via Email</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Successful</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Unsuccessful</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call via Phone</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Phone Call</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Site Visit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Group Email</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Payment Delivery</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Incoming</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Outgoing</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>06/15/2026 - 06/21/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>215</v>
+      </c>
+      <c r="O2" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P2" s="4" t="inlineStr"/>
+      <c r="Q2" s="4" t="inlineStr"/>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
+      <c r="T2" s="5" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>06/15/2026 - 06/21/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="P3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" s="8" t="inlineStr"/>
+      <c r="T3" s="5" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>06/15/2026 - 06/21/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>JR Scappini</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" s="5" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>06/15/2026 - 06/21/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr"/>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="inlineStr"/>
+      <c r="T5" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>06/15/2026 - 06/21/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 06/15/2026 - 06/21/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" s="5" t="n">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>06/22/2026 - 06/28/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="4" t="inlineStr"/>
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr"/>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr"/>
+      <c r="T8" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>06/22/2026 - 06/28/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr"/>
+      <c r="D9" s="8" t="inlineStr"/>
+      <c r="E9" s="8" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr"/>
+      <c r="G9" s="8" t="inlineStr"/>
+      <c r="H9" s="8" t="inlineStr"/>
+      <c r="I9" s="8" t="inlineStr"/>
+      <c r="J9" s="8" t="inlineStr"/>
+      <c r="K9" s="8" t="inlineStr"/>
+      <c r="L9" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" s="8" t="inlineStr"/>
+      <c r="N9" s="8" t="inlineStr"/>
+      <c r="O9" s="8" t="inlineStr"/>
+      <c r="P9" s="8" t="inlineStr"/>
+      <c r="Q9" s="8" t="inlineStr"/>
+      <c r="R9" s="8" t="inlineStr"/>
+      <c r="S9" s="8" t="inlineStr"/>
+      <c r="T9" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>06/22/2026 - 06/28/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" s="4" t="inlineStr"/>
+      <c r="L10" s="4" t="inlineStr"/>
+      <c r="M10" s="4" t="inlineStr"/>
+      <c r="N10" s="4" t="inlineStr"/>
+      <c r="O10" s="4" t="inlineStr"/>
+      <c r="P10" s="4" t="inlineStr"/>
+      <c r="Q10" s="4" t="inlineStr"/>
+      <c r="R10" s="4" t="inlineStr"/>
+      <c r="S10" s="4" t="inlineStr"/>
+      <c r="T10" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 06/22/2026 - 06/28/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+      <c r="R11" s="5" t="inlineStr"/>
+      <c r="S11" s="5" t="inlineStr"/>
+      <c r="T11" s="5" t="n">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A7:B7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/master_activity.xlsx
+++ b/master_activity.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Wk 06-01-2026" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Wk 06-08-2026" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Wk 06-15-2026" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Wk 06-22-2026" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Weeks'!$A$1:$T$1</definedName>
@@ -523,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T22"/>
+  <dimension ref="A1:T27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1274,11 +1275,7 @@
           <t>06/15/2026 - 06/21/2026</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>JR Scappini</t>
-        </is>
-      </c>
+      <c r="B15" s="10" t="n"/>
       <c r="C15" s="8" t="inlineStr"/>
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="8" t="n">
@@ -1455,31 +1452,43 @@
       </c>
       <c r="C19" s="8" t="inlineStr"/>
       <c r="D19" s="8" t="inlineStr"/>
-      <c r="E19" s="8" t="inlineStr"/>
-      <c r="F19" s="8" t="inlineStr"/>
-      <c r="G19" s="8" t="inlineStr"/>
+      <c r="E19" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>20</v>
+      </c>
       <c r="H19" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" s="8" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>52</v>
+      </c>
       <c r="L19" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" s="8" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>61</v>
+      </c>
       <c r="N19" s="8" t="inlineStr"/>
-      <c r="O19" s="8" t="inlineStr"/>
+      <c r="O19" s="8" t="n">
+        <v>6</v>
+      </c>
       <c r="P19" s="8" t="inlineStr"/>
       <c r="Q19" s="8" t="inlineStr"/>
       <c r="R19" s="8" t="inlineStr"/>
       <c r="S19" s="8" t="inlineStr"/>
       <c r="T19" s="5" t="n">
-        <v>7</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
@@ -1490,30 +1499,48 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Michael Petrick</t>
+          <t>Christine Mello</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
-      <c r="D20" s="4" t="inlineStr"/>
+      <c r="D20" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="E20" s="4" t="inlineStr"/>
       <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr"/>
-      <c r="I20" s="4" t="inlineStr"/>
-      <c r="J20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="K20" s="4" t="inlineStr"/>
-      <c r="L20" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" s="4" t="inlineStr"/>
+      <c r="L20" s="4" t="inlineStr"/>
+      <c r="M20" s="4" t="n">
+        <v>10</v>
+      </c>
       <c r="N20" s="4" t="inlineStr"/>
-      <c r="O20" s="4" t="inlineStr"/>
-      <c r="P20" s="4" t="inlineStr"/>
+      <c r="O20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="Q20" s="4" t="inlineStr"/>
-      <c r="R20" s="4" t="inlineStr"/>
-      <c r="S20" s="4" t="inlineStr"/>
+      <c r="R20" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="S20" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="T20" s="5" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
@@ -1524,21 +1551,19 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Roger Guzowski</t>
+          <t>JR Scappini</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr"/>
       <c r="D21" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" s="8" t="inlineStr"/>
       <c r="F21" s="8" t="inlineStr"/>
       <c r="G21" s="8" t="inlineStr"/>
       <c r="H21" s="8" t="inlineStr"/>
       <c r="I21" s="8" t="inlineStr"/>
-      <c r="J21" s="8" t="n">
-        <v>3</v>
-      </c>
+      <c r="J21" s="8" t="inlineStr"/>
       <c r="K21" s="8" t="inlineStr"/>
       <c r="L21" s="8" t="inlineStr"/>
       <c r="M21" s="8" t="inlineStr"/>
@@ -1549,54 +1574,276 @@
       <c r="R21" s="8" t="inlineStr"/>
       <c r="S21" s="8" t="inlineStr"/>
       <c r="T21" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>06/22/2026 - 06/28/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr"/>
+      <c r="J22" s="4" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr"/>
+      <c r="L22" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N22" s="4" t="inlineStr"/>
+      <c r="O22" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="P22" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R22" s="4" t="inlineStr"/>
+      <c r="S22" s="4" t="inlineStr"/>
+      <c r="T22" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>06/22/2026 - 06/28/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr"/>
+      <c r="D23" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" s="8" t="inlineStr"/>
+      <c r="F23" s="8" t="inlineStr"/>
+      <c r="G23" s="8" t="inlineStr"/>
+      <c r="H23" s="8" t="inlineStr"/>
+      <c r="I23" s="8" t="inlineStr"/>
+      <c r="J23" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" s="8" t="inlineStr"/>
+      <c r="L23" s="8" t="inlineStr"/>
+      <c r="M23" s="8" t="inlineStr"/>
+      <c r="N23" s="8" t="inlineStr"/>
+      <c r="O23" s="8" t="inlineStr"/>
+      <c r="P23" s="8" t="inlineStr"/>
+      <c r="Q23" s="8" t="inlineStr"/>
+      <c r="R23" s="8" t="inlineStr"/>
+      <c r="S23" s="8" t="inlineStr"/>
+      <c r="T23" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 06/22/2026 - 06/28/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="P24" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q24" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R24" s="5" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>WEEK TOTAL — 06/22/2026 - 06/28/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="5" t="n">
+      <c r="S24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" s="5" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>06/29/2026 - 07/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr"/>
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J22" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="K22" s="5" t="inlineStr"/>
-      <c r="L22" s="5" t="n">
+      <c r="G25" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" s="8" t="inlineStr"/>
+      <c r="I25" s="8" t="inlineStr"/>
+      <c r="J25" s="8" t="inlineStr"/>
+      <c r="K25" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M25" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" s="8" t="inlineStr"/>
+      <c r="O25" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" s="8" t="inlineStr"/>
+      <c r="Q25" s="8" t="inlineStr"/>
+      <c r="R25" s="8" t="inlineStr"/>
+      <c r="S25" s="8" t="inlineStr"/>
+      <c r="T25" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>06/29/2026 - 07/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr"/>
+      <c r="D26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" s="4" t="inlineStr"/>
+      <c r="J26" s="4" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr"/>
+      <c r="L26" s="4" t="inlineStr"/>
+      <c r="M26" s="4" t="inlineStr"/>
+      <c r="N26" s="4" t="inlineStr"/>
+      <c r="O26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" s="4" t="inlineStr"/>
+      <c r="Q26" s="4" t="inlineStr"/>
+      <c r="R26" s="4" t="inlineStr"/>
+      <c r="S26" s="4" t="inlineStr"/>
+      <c r="T26" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 06/29/2026 - 07/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="M22" s="5" t="inlineStr"/>
-      <c r="N22" s="5" t="inlineStr"/>
-      <c r="O22" s="5" t="inlineStr"/>
-      <c r="P22" s="5" t="inlineStr"/>
-      <c r="Q22" s="5" t="inlineStr"/>
-      <c r="R22" s="5" t="inlineStr"/>
-      <c r="S22" s="5" t="inlineStr"/>
-      <c r="T22" s="5" t="n">
-        <v>14</v>
+      <c r="G27" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+      <c r="R27" s="5" t="inlineStr"/>
+      <c r="S27" s="5" t="inlineStr"/>
+      <c r="T27" s="5" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="A24:B24"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A27:B27"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A12:B12"/>
   </mergeCells>
@@ -3206,4 +3453,542 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Activity/General Notes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Completed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Scheduled</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Via Email</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Successful</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Unsuccessful</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call via Phone</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Phone Call</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Site Visit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Group Email</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Payment Delivery</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Incoming</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Outgoing</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>06/22/2026 - 06/28/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="N2" s="4" t="inlineStr"/>
+      <c r="O2" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P2" s="4" t="inlineStr"/>
+      <c r="Q2" s="4" t="inlineStr"/>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
+      <c r="T2" s="5" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>06/22/2026 - 06/28/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="8" t="inlineStr"/>
+      <c r="M3" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="8" t="inlineStr"/>
+      <c r="R3" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="S3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="5" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>06/22/2026 - 06/28/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>JR Scappini</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>06/22/2026 - 06/28/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr"/>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="P5" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="inlineStr"/>
+      <c r="T5" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>06/22/2026 - 06/28/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 06/22/2026 - 06/28/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="S7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" s="5" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>06/29/2026 - 07/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr"/>
+      <c r="T8" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>06/29/2026 - 07/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr"/>
+      <c r="D9" s="8" t="inlineStr"/>
+      <c r="E9" s="8" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr"/>
+      <c r="G9" s="8" t="inlineStr"/>
+      <c r="H9" s="8" t="inlineStr"/>
+      <c r="I9" s="8" t="inlineStr"/>
+      <c r="J9" s="8" t="inlineStr"/>
+      <c r="K9" s="8" t="inlineStr"/>
+      <c r="L9" s="8" t="inlineStr"/>
+      <c r="M9" s="8" t="inlineStr"/>
+      <c r="N9" s="8" t="inlineStr"/>
+      <c r="O9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" s="8" t="inlineStr"/>
+      <c r="Q9" s="8" t="inlineStr"/>
+      <c r="R9" s="8" t="inlineStr"/>
+      <c r="S9" s="8" t="inlineStr"/>
+      <c r="T9" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 06/29/2026 - 07/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+      <c r="R10" s="5" t="inlineStr"/>
+      <c r="S10" s="5" t="inlineStr"/>
+      <c r="T10" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A7:B7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/master_activity.xlsx
+++ b/master_activity.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Wk 06-08-2026" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Wk 06-15-2026" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Wk 06-22-2026" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Wk 06-29-2026" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Weeks'!$A$1:$T$1</definedName>
@@ -524,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T27"/>
+  <dimension ref="A1:T30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1583,11 +1584,7 @@
           <t>06/22/2026 - 06/28/2026</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Michael Petrick</t>
-        </is>
-      </c>
+      <c r="B22" s="10" t="n"/>
       <c r="C22" s="4" t="inlineStr"/>
       <c r="D22" s="4" t="inlineStr"/>
       <c r="E22" s="4" t="inlineStr"/>
@@ -1727,10 +1724,10 @@
       <c r="C25" s="8" t="inlineStr"/>
       <c r="D25" s="8" t="inlineStr"/>
       <c r="E25" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G25" s="8" t="n">
         <v>2</v>
@@ -1739,24 +1736,24 @@
       <c r="I25" s="8" t="inlineStr"/>
       <c r="J25" s="8" t="inlineStr"/>
       <c r="K25" s="8" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="N25" s="8" t="inlineStr"/>
       <c r="O25" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P25" s="8" t="inlineStr"/>
       <c r="Q25" s="8" t="inlineStr"/>
       <c r="R25" s="8" t="inlineStr"/>
       <c r="S25" s="8" t="inlineStr"/>
       <c r="T25" s="5" t="n">
-        <v>16</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
@@ -1767,78 +1764,211 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Michael Petrick</t>
+          <t>Christine Mello</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
-      <c r="D26" s="4" t="inlineStr"/>
-      <c r="E26" s="4" t="inlineStr"/>
+      <c r="D26" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr"/>
-      <c r="H26" s="4" t="inlineStr"/>
-      <c r="I26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="J26" s="4" t="inlineStr"/>
       <c r="K26" s="4" t="inlineStr"/>
       <c r="L26" s="4" t="inlineStr"/>
       <c r="M26" s="4" t="inlineStr"/>
       <c r="N26" s="4" t="inlineStr"/>
-      <c r="O26" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="O26" s="4" t="inlineStr"/>
       <c r="P26" s="4" t="inlineStr"/>
-      <c r="Q26" s="4" t="inlineStr"/>
-      <c r="R26" s="4" t="inlineStr"/>
-      <c r="S26" s="4" t="inlineStr"/>
+      <c r="Q26" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="T26" s="5" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>06/29/2026 - 07/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>JR Scappini</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr"/>
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="8" t="inlineStr"/>
+      <c r="F27" s="8" t="inlineStr"/>
+      <c r="G27" s="8" t="inlineStr"/>
+      <c r="H27" s="8" t="inlineStr"/>
+      <c r="I27" s="8" t="inlineStr"/>
+      <c r="J27" s="8" t="inlineStr"/>
+      <c r="K27" s="8" t="inlineStr"/>
+      <c r="L27" s="8" t="inlineStr"/>
+      <c r="M27" s="8" t="inlineStr"/>
+      <c r="N27" s="8" t="inlineStr"/>
+      <c r="O27" s="8" t="inlineStr"/>
+      <c r="P27" s="8" t="inlineStr"/>
+      <c r="Q27" s="8" t="inlineStr"/>
+      <c r="R27" s="8" t="inlineStr"/>
+      <c r="S27" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="T27" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>06/29/2026 - 07/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" s="4" t="inlineStr"/>
+      <c r="J28" s="4" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr"/>
+      <c r="L28" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M28" s="4" t="inlineStr"/>
+      <c r="N28" s="4" t="inlineStr"/>
+      <c r="O28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" s="4" t="inlineStr"/>
+      <c r="Q28" s="4" t="inlineStr"/>
+      <c r="R28" s="4" t="inlineStr"/>
+      <c r="S28" s="4" t="inlineStr"/>
+      <c r="T28" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>06/29/2026 - 07/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="n">
+        <v>1739</v>
+      </c>
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="8" t="inlineStr"/>
+      <c r="F29" s="8" t="inlineStr"/>
+      <c r="G29" s="8" t="inlineStr"/>
+      <c r="H29" s="8" t="inlineStr"/>
+      <c r="I29" s="8" t="inlineStr"/>
+      <c r="J29" s="8" t="inlineStr"/>
+      <c r="K29" s="8" t="inlineStr"/>
+      <c r="L29" s="8" t="inlineStr"/>
+      <c r="M29" s="8" t="inlineStr"/>
+      <c r="N29" s="8" t="inlineStr"/>
+      <c r="O29" s="8" t="inlineStr"/>
+      <c r="P29" s="8" t="inlineStr"/>
+      <c r="Q29" s="8" t="inlineStr"/>
+      <c r="R29" s="8" t="inlineStr"/>
+      <c r="S29" s="8" t="inlineStr"/>
+      <c r="T29" s="5" t="n">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>WEEK TOTAL — 06/29/2026 - 07/05/2026</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="5" t="inlineStr"/>
-      <c r="D27" s="5" t="inlineStr"/>
-      <c r="E27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="5" t="n">
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="5" t="n">
+        <v>1739</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="G27" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H27" s="5" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr"/>
-      <c r="K27" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="L27" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" s="5" t="inlineStr"/>
-      <c r="O27" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="P27" s="5" t="inlineStr"/>
-      <c r="Q27" s="5" t="inlineStr"/>
-      <c r="R27" s="5" t="inlineStr"/>
-      <c r="S27" s="5" t="inlineStr"/>
-      <c r="T27" s="5" t="n">
-        <v>17</v>
+      <c r="P30" s="5" t="inlineStr"/>
+      <c r="Q30" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="T30" s="5" t="n">
+        <v>1851</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A30:B30"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A10:B10"/>
@@ -3991,4 +4121,399 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Activity/General Notes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Completed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Scheduled</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Via Email</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Successful</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Unsuccessful</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call via Phone</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Phone Call</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Site Visit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Group Email</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Payment Delivery</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Incoming</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Outgoing</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>06/29/2026 - 07/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="4" t="inlineStr"/>
+      <c r="J2" s="4" t="inlineStr"/>
+      <c r="K2" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="N2" s="4" t="inlineStr"/>
+      <c r="O2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P2" s="4" t="inlineStr"/>
+      <c r="Q2" s="4" t="inlineStr"/>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
+      <c r="T2" s="5" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>06/29/2026 - 07/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="8" t="inlineStr"/>
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="inlineStr"/>
+      <c r="P3" s="8" t="inlineStr"/>
+      <c r="Q3" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" s="5" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>06/29/2026 - 07/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>JR Scappini</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="T4" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>06/29/2026 - 07/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr"/>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="inlineStr"/>
+      <c r="T5" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>06/29/2026 - 07/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>1739</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="5" t="n">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 06/29/2026 - 07/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="5" t="n">
+        <v>1739</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="T7" s="5" t="n">
+        <v>1851</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A7:B7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/master_activity.xlsx
+++ b/master_activity.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Wk 06-15-2026" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Wk 06-22-2026" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Wk 06-29-2026" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Wk 07-06-2026" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Weeks'!$A$1:$T$1</definedName>
@@ -525,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T30"/>
+  <dimension ref="A1:T36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1810,11 +1811,7 @@
           <t>06/29/2026 - 07/05/2026</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>JR Scappini</t>
-        </is>
-      </c>
+      <c r="B27" s="10" t="n"/>
       <c r="C27" s="8" t="inlineStr"/>
       <c r="D27" s="8" t="inlineStr"/>
       <c r="E27" s="8" t="inlineStr"/>
@@ -1964,17 +1961,275 @@
         <v>1851</v>
       </c>
     </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>07/06/2026 - 07/12/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr"/>
+      <c r="D31" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="E31" s="8" t="inlineStr"/>
+      <c r="F31" s="8" t="inlineStr"/>
+      <c r="G31" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I31" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J31" s="8" t="inlineStr"/>
+      <c r="K31" s="8" t="inlineStr"/>
+      <c r="L31" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M31" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N31" s="8" t="inlineStr"/>
+      <c r="O31" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P31" s="8" t="inlineStr"/>
+      <c r="Q31" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S31" s="8" t="inlineStr"/>
+      <c r="T31" s="5" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>07/06/2026 - 07/12/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr"/>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr"/>
+      <c r="H32" s="4" t="inlineStr"/>
+      <c r="I32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M32" s="4" t="inlineStr"/>
+      <c r="N32" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="O32" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P32" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="4" t="inlineStr"/>
+      <c r="R32" s="4" t="inlineStr"/>
+      <c r="S32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" s="5" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>07/06/2026 - 07/12/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr"/>
+      <c r="D33" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="E33" s="8" t="inlineStr"/>
+      <c r="F33" s="8" t="inlineStr"/>
+      <c r="G33" s="8" t="inlineStr"/>
+      <c r="H33" s="8" t="inlineStr"/>
+      <c r="I33" s="8" t="inlineStr"/>
+      <c r="J33" s="8" t="inlineStr"/>
+      <c r="K33" s="8" t="inlineStr"/>
+      <c r="L33" s="8" t="inlineStr"/>
+      <c r="M33" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N33" s="8" t="inlineStr"/>
+      <c r="O33" s="8" t="inlineStr"/>
+      <c r="P33" s="8" t="inlineStr"/>
+      <c r="Q33" s="8" t="inlineStr"/>
+      <c r="R33" s="8" t="inlineStr"/>
+      <c r="S33" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T33" s="5" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 07/06/2026 - 07/12/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="5" t="inlineStr"/>
+      <c r="D34" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="S34" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T34" s="5" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>07/13/2026 - 07/19/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr"/>
+      <c r="D35" s="8" t="inlineStr"/>
+      <c r="E35" s="8" t="inlineStr"/>
+      <c r="F35" s="8" t="inlineStr"/>
+      <c r="G35" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H35" s="8" t="inlineStr"/>
+      <c r="I35" s="8" t="inlineStr"/>
+      <c r="J35" s="8" t="inlineStr"/>
+      <c r="K35" s="8" t="inlineStr"/>
+      <c r="L35" s="8" t="inlineStr"/>
+      <c r="M35" s="8" t="inlineStr"/>
+      <c r="N35" s="8" t="inlineStr"/>
+      <c r="O35" s="8" t="inlineStr"/>
+      <c r="P35" s="8" t="inlineStr"/>
+      <c r="Q35" s="8" t="inlineStr"/>
+      <c r="R35" s="8" t="inlineStr"/>
+      <c r="S35" s="8" t="inlineStr"/>
+      <c r="T35" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 07/13/2026 - 07/19/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="5" t="inlineStr"/>
+      <c r="D36" s="5" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H36" s="5" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr"/>
+      <c r="L36" s="5" t="inlineStr"/>
+      <c r="M36" s="5" t="inlineStr"/>
+      <c r="N36" s="5" t="inlineStr"/>
+      <c r="O36" s="5" t="inlineStr"/>
+      <c r="P36" s="5" t="inlineStr"/>
+      <c r="Q36" s="5" t="inlineStr"/>
+      <c r="R36" s="5" t="inlineStr"/>
+      <c r="S36" s="5" t="inlineStr"/>
+      <c r="T36" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <mergeCells count="9">
+  <mergeCells count="11">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A36:B36"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A34:B34"/>
     <mergeCell ref="A12:B12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4516,4 +4771,402 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Activity/General Notes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Completed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Scheduled</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Via Email</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Successful</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Unsuccessful</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call via Phone</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Phone Call</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Site Visit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Group Email</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Payment Delivery</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Incoming</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Outgoing</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>07/06/2026 - 07/12/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr"/>
+      <c r="K2" s="4" t="inlineStr"/>
+      <c r="L2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N2" s="4" t="inlineStr"/>
+      <c r="O2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P2" s="4" t="inlineStr"/>
+      <c r="Q2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S2" s="4" t="inlineStr"/>
+      <c r="T2" s="5" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>07/06/2026 - 07/12/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="8" t="inlineStr"/>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr"/>
+      <c r="H3" s="8" t="inlineStr"/>
+      <c r="I3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="K3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="O3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="8" t="inlineStr"/>
+      <c r="R3" s="8" t="inlineStr"/>
+      <c r="S3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="5" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>07/06/2026 - 07/12/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" s="5" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 07/06/2026 - 07/12/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>07/13/2026 - 07/19/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 07/13/2026 - 07/19/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr"/>
+      <c r="S7" s="5" t="inlineStr"/>
+      <c r="T7" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A5:B5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/master_activity.xlsx
+++ b/master_activity.xlsx
@@ -14,6 +14,7 @@
     <sheet name="Wk 06-22-2026" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Wk 06-29-2026" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Wk 07-06-2026" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Wk 07-13-2026" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Weeks'!$A$1:$T$1</definedName>
@@ -526,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T36"/>
+  <dimension ref="A1:T39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2161,71 +2162,258 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Christine Mello</t>
+          <t>Carlos Casillas</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr"/>
       <c r="D35" s="8" t="inlineStr"/>
-      <c r="E35" s="8" t="inlineStr"/>
-      <c r="F35" s="8" t="inlineStr"/>
+      <c r="E35" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>16</v>
+      </c>
       <c r="G35" s="8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H35" s="8" t="inlineStr"/>
-      <c r="I35" s="8" t="inlineStr"/>
-      <c r="J35" s="8" t="inlineStr"/>
-      <c r="K35" s="8" t="inlineStr"/>
-      <c r="L35" s="8" t="inlineStr"/>
-      <c r="M35" s="8" t="inlineStr"/>
+      <c r="I35" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="K35" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="L35" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M35" s="8" t="n">
+        <v>73</v>
+      </c>
       <c r="N35" s="8" t="inlineStr"/>
-      <c r="O35" s="8" t="inlineStr"/>
+      <c r="O35" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="P35" s="8" t="inlineStr"/>
       <c r="Q35" s="8" t="inlineStr"/>
       <c r="R35" s="8" t="inlineStr"/>
       <c r="S35" s="8" t="inlineStr"/>
       <c r="T35" s="5" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>07/13/2026 - 07/19/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
+      <c r="G36" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr"/>
+      <c r="K36" s="4" t="inlineStr"/>
+      <c r="L36" s="4" t="inlineStr"/>
+      <c r="M36" s="4" t="inlineStr"/>
+      <c r="N36" s="4" t="inlineStr"/>
+      <c r="O36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S36" s="4" t="inlineStr"/>
+      <c r="T36" s="5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>07/13/2026 - 07/19/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr"/>
+      <c r="D37" s="8" t="inlineStr"/>
+      <c r="E37" s="8" t="inlineStr"/>
+      <c r="F37" s="8" t="inlineStr"/>
+      <c r="G37" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H37" s="8" t="inlineStr"/>
+      <c r="I37" s="8" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="J37" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L37" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N37" s="8" t="n">
+        <v>276</v>
+      </c>
+      <c r="O37" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="8" t="inlineStr"/>
+      <c r="R37" s="8" t="inlineStr"/>
+      <c r="S37" s="8" t="inlineStr"/>
+      <c r="T37" s="5" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>07/13/2026 - 07/19/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr"/>
+      <c r="D38" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="4" t="inlineStr"/>
+      <c r="J38" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K38" s="4" t="inlineStr"/>
+      <c r="L38" s="4" t="inlineStr"/>
+      <c r="M38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" s="4" t="inlineStr"/>
+      <c r="O38" s="4" t="inlineStr"/>
+      <c r="P38" s="4" t="inlineStr"/>
+      <c r="Q38" s="4" t="inlineStr"/>
+      <c r="R38" s="4" t="inlineStr"/>
+      <c r="S38" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="T38" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>WEEK TOTAL — 07/13/2026 - 07/19/2026</t>
         </is>
       </c>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="5" t="inlineStr"/>
-      <c r="D36" s="5" t="inlineStr"/>
-      <c r="E36" s="5" t="inlineStr"/>
-      <c r="F36" s="5" t="inlineStr"/>
-      <c r="G36" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="H36" s="5" t="inlineStr"/>
-      <c r="I36" s="5" t="inlineStr"/>
-      <c r="J36" s="5" t="inlineStr"/>
-      <c r="K36" s="5" t="inlineStr"/>
-      <c r="L36" s="5" t="inlineStr"/>
-      <c r="M36" s="5" t="inlineStr"/>
-      <c r="N36" s="5" t="inlineStr"/>
-      <c r="O36" s="5" t="inlineStr"/>
-      <c r="P36" s="5" t="inlineStr"/>
-      <c r="Q36" s="5" t="inlineStr"/>
-      <c r="R36" s="5" t="inlineStr"/>
-      <c r="S36" s="5" t="inlineStr"/>
-      <c r="T36" s="5" t="n">
-        <v>7</v>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="5" t="inlineStr"/>
+      <c r="D39" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="N39" s="5" t="n">
+        <v>276</v>
+      </c>
+      <c r="O39" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="P39" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R39" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S39" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="T39" s="5" t="n">
+        <v>567</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A39:B39"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A22:B22"/>
@@ -5169,4 +5357,395 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Activity/General Notes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Completed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Scheduled</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Via Email</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Successful</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Unsuccessful</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call via Phone</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Phone Call</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Site Visit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Group Email</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Payment Delivery</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Incoming</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Outgoing</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>07/13/2026 - 07/19/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="N2" s="4" t="inlineStr"/>
+      <c r="O2" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="P2" s="4" t="inlineStr"/>
+      <c r="Q2" s="4" t="inlineStr"/>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
+      <c r="T2" s="5" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>07/13/2026 - 07/19/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="8" t="inlineStr"/>
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" s="8" t="inlineStr"/>
+      <c r="T3" s="5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>07/13/2026 - 07/19/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>276</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="5" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>07/13/2026 - 07/19/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="8" t="inlineStr"/>
+      <c r="M5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 07/13/2026 - 07/19/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>276</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>567</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:B6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/master_activity.xlsx
+++ b/master_activity.xlsx
@@ -15,6 +15,7 @@
     <sheet name="Wk 06-29-2026" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Wk 07-06-2026" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Wk 07-13-2026" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Wk 07-20-2026" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Weeks'!$A$1:$T$1</definedName>
@@ -527,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T39"/>
+  <dimension ref="A1:T47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2210,11 +2211,7 @@
           <t>07/13/2026 - 07/19/2026</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Christine Mello</t>
-        </is>
-      </c>
+      <c r="B36" s="10" t="n"/>
       <c r="C36" s="4" t="inlineStr"/>
       <c r="D36" s="4" t="n">
         <v>9</v>
@@ -2404,14 +2401,344 @@
         <v>567</v>
       </c>
     </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>07/20/2026 - 07/26/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr"/>
+      <c r="J40" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K40" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="M40" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="N40" s="4" t="inlineStr"/>
+      <c r="O40" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P40" s="4" t="inlineStr"/>
+      <c r="Q40" s="4" t="inlineStr"/>
+      <c r="R40" s="4" t="inlineStr"/>
+      <c r="S40" s="4" t="inlineStr"/>
+      <c r="T40" s="5" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>07/20/2026 - 07/26/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Harrison Shr</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr"/>
+      <c r="D41" s="8" t="inlineStr"/>
+      <c r="E41" s="8" t="inlineStr"/>
+      <c r="F41" s="8" t="inlineStr"/>
+      <c r="G41" s="8" t="inlineStr"/>
+      <c r="H41" s="8" t="inlineStr"/>
+      <c r="I41" s="8" t="inlineStr"/>
+      <c r="J41" s="8" t="inlineStr"/>
+      <c r="K41" s="8" t="inlineStr"/>
+      <c r="L41" s="8" t="inlineStr"/>
+      <c r="M41" s="8" t="inlineStr"/>
+      <c r="N41" s="8" t="inlineStr"/>
+      <c r="O41" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P41" s="8" t="inlineStr"/>
+      <c r="Q41" s="8" t="inlineStr"/>
+      <c r="R41" s="8" t="inlineStr"/>
+      <c r="S41" s="8" t="inlineStr"/>
+      <c r="T41" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>07/20/2026 - 07/26/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>JR Scappini</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr"/>
+      <c r="D42" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr"/>
+      <c r="H42" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" s="4" t="inlineStr"/>
+      <c r="J42" s="4" t="inlineStr"/>
+      <c r="K42" s="4" t="inlineStr"/>
+      <c r="L42" s="4" t="inlineStr"/>
+      <c r="M42" s="4" t="inlineStr"/>
+      <c r="N42" s="4" t="inlineStr"/>
+      <c r="O42" s="4" t="inlineStr"/>
+      <c r="P42" s="4" t="inlineStr"/>
+      <c r="Q42" s="4" t="inlineStr"/>
+      <c r="R42" s="4" t="inlineStr"/>
+      <c r="S42" s="4" t="inlineStr"/>
+      <c r="T42" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>07/20/2026 - 07/26/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr"/>
+      <c r="D43" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" s="8" t="inlineStr"/>
+      <c r="F43" s="8" t="inlineStr"/>
+      <c r="G43" s="8" t="inlineStr"/>
+      <c r="H43" s="8" t="inlineStr"/>
+      <c r="I43" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" s="8" t="inlineStr"/>
+      <c r="K43" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L43" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="M43" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N43" s="8" t="inlineStr"/>
+      <c r="O43" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P43" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R43" s="8" t="inlineStr"/>
+      <c r="S43" s="8" t="inlineStr"/>
+      <c r="T43" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>07/20/2026 - 07/26/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr"/>
+      <c r="D44" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
+      <c r="G44" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" s="4" t="inlineStr"/>
+      <c r="J44" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K44" s="4" t="inlineStr"/>
+      <c r="L44" s="4" t="inlineStr"/>
+      <c r="M44" s="4" t="inlineStr"/>
+      <c r="N44" s="4" t="inlineStr"/>
+      <c r="O44" s="4" t="inlineStr"/>
+      <c r="P44" s="4" t="inlineStr"/>
+      <c r="Q44" s="4" t="inlineStr"/>
+      <c r="R44" s="4" t="inlineStr"/>
+      <c r="S44" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T44" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 07/20/2026 - 07/26/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="5" t="inlineStr"/>
+      <c r="D45" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M45" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="N45" s="5" t="inlineStr"/>
+      <c r="O45" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="P45" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R45" s="5" t="inlineStr"/>
+      <c r="S45" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T45" s="5" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>07/27/2026 - 08/02/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr"/>
+      <c r="D46" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr"/>
+      <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" s="4" t="inlineStr"/>
+      <c r="J46" s="4" t="inlineStr"/>
+      <c r="K46" s="4" t="inlineStr"/>
+      <c r="L46" s="4" t="inlineStr"/>
+      <c r="M46" s="4" t="inlineStr"/>
+      <c r="N46" s="4" t="inlineStr"/>
+      <c r="O46" s="4" t="inlineStr"/>
+      <c r="P46" s="4" t="inlineStr"/>
+      <c r="Q46" s="4" t="inlineStr"/>
+      <c r="R46" s="4" t="inlineStr"/>
+      <c r="S46" s="4" t="inlineStr"/>
+      <c r="T46" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 07/27/2026 - 08/02/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="5" t="inlineStr"/>
+      <c r="D47" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" s="5" t="inlineStr"/>
+      <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="5" t="inlineStr"/>
+      <c r="H47" s="5" t="inlineStr"/>
+      <c r="I47" s="5" t="inlineStr"/>
+      <c r="J47" s="5" t="inlineStr"/>
+      <c r="K47" s="5" t="inlineStr"/>
+      <c r="L47" s="5" t="inlineStr"/>
+      <c r="M47" s="5" t="inlineStr"/>
+      <c r="N47" s="5" t="inlineStr"/>
+      <c r="O47" s="5" t="inlineStr"/>
+      <c r="P47" s="5" t="inlineStr"/>
+      <c r="Q47" s="5" t="inlineStr"/>
+      <c r="R47" s="5" t="inlineStr"/>
+      <c r="S47" s="5" t="inlineStr"/>
+      <c r="T47" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <mergeCells count="12">
+  <mergeCells count="14">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A47:B47"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A18:B18"/>
@@ -5748,4 +6075,474 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Activity/General Notes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Completed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Scheduled</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Via Email</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Successful</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Unsuccessful</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call via Phone</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Phone Call</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Site Visit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Group Email</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Payment Delivery</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Incoming</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Outgoing</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>07/20/2026 - 07/26/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="4" t="inlineStr"/>
+      <c r="J2" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="N2" s="4" t="inlineStr"/>
+      <c r="O2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P2" s="4" t="inlineStr"/>
+      <c r="Q2" s="4" t="inlineStr"/>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
+      <c r="T2" s="5" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>07/20/2026 - 07/26/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Harrison Shr</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="8" t="inlineStr"/>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr"/>
+      <c r="H3" s="8" t="inlineStr"/>
+      <c r="I3" s="8" t="inlineStr"/>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="8" t="inlineStr"/>
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" s="8" t="inlineStr"/>
+      <c r="Q3" s="8" t="inlineStr"/>
+      <c r="R3" s="8" t="inlineStr"/>
+      <c r="S3" s="8" t="inlineStr"/>
+      <c r="T3" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>07/20/2026 - 07/26/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>JR Scappini</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>07/20/2026 - 07/26/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="inlineStr"/>
+      <c r="T5" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>07/20/2026 - 07/26/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 07/20/2026 - 07/26/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="5" t="inlineStr"/>
+      <c r="D7" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="5" t="inlineStr"/>
+      <c r="S7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" s="5" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>07/27/2026 - 08/02/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="inlineStr"/>
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr"/>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr"/>
+      <c r="T8" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 07/27/2026 - 08/02/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr"/>
+      <c r="S9" s="5" t="inlineStr"/>
+      <c r="T9" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A7:B7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/master_activity.xlsx
+++ b/master_activity.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Wk 07-06-2026" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Wk 07-13-2026" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Wk 07-20-2026" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Wk 07-27-2026" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Weeks'!$A$1:$T$1</definedName>
@@ -528,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T47"/>
+  <dimension ref="A1:T50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2673,69 +2674,250 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Roger Guzowski</t>
+          <t>Carlos Casillas</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr"/>
       <c r="D46" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E46" s="4" t="inlineStr"/>
-      <c r="F46" s="4" t="inlineStr"/>
-      <c r="G46" s="4" t="inlineStr"/>
-      <c r="H46" s="4" t="inlineStr"/>
-      <c r="I46" s="4" t="inlineStr"/>
-      <c r="J46" s="4" t="inlineStr"/>
-      <c r="K46" s="4" t="inlineStr"/>
-      <c r="L46" s="4" t="inlineStr"/>
-      <c r="M46" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K46" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="L46" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="M46" s="4" t="n">
+        <v>52</v>
+      </c>
       <c r="N46" s="4" t="inlineStr"/>
-      <c r="O46" s="4" t="inlineStr"/>
+      <c r="O46" s="4" t="n">
+        <v>12</v>
+      </c>
       <c r="P46" s="4" t="inlineStr"/>
       <c r="Q46" s="4" t="inlineStr"/>
       <c r="R46" s="4" t="inlineStr"/>
-      <c r="S46" s="4" t="inlineStr"/>
+      <c r="S46" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="T46" s="5" t="n">
-        <v>2</v>
+        <v>186</v>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>07/27/2026 - 08/02/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr"/>
+      <c r="D47" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E47" s="8" t="inlineStr"/>
+      <c r="F47" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I47" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J47" s="8" t="inlineStr"/>
+      <c r="K47" s="8" t="inlineStr"/>
+      <c r="L47" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N47" s="8" t="inlineStr"/>
+      <c r="O47" s="8" t="inlineStr"/>
+      <c r="P47" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q47" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R47" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S47" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="T47" s="5" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>07/27/2026 - 08/02/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>JR Scappini</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr"/>
+      <c r="D48" s="4" t="inlineStr"/>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr"/>
+      <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" s="4" t="inlineStr"/>
+      <c r="J48" s="4" t="inlineStr"/>
+      <c r="K48" s="4" t="inlineStr"/>
+      <c r="L48" s="4" t="inlineStr"/>
+      <c r="M48" s="4" t="inlineStr"/>
+      <c r="N48" s="4" t="inlineStr"/>
+      <c r="O48" s="4" t="inlineStr"/>
+      <c r="P48" s="4" t="inlineStr"/>
+      <c r="Q48" s="4" t="inlineStr"/>
+      <c r="R48" s="4" t="inlineStr"/>
+      <c r="S48" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T48" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>07/27/2026 - 08/02/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr"/>
+      <c r="D49" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="8" t="inlineStr"/>
+      <c r="G49" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="8" t="inlineStr"/>
+      <c r="I49" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="8" t="inlineStr"/>
+      <c r="K49" s="8" t="inlineStr"/>
+      <c r="L49" s="8" t="inlineStr"/>
+      <c r="M49" s="8" t="inlineStr"/>
+      <c r="N49" s="8" t="inlineStr"/>
+      <c r="O49" s="8" t="inlineStr"/>
+      <c r="P49" s="8" t="inlineStr"/>
+      <c r="Q49" s="8" t="inlineStr"/>
+      <c r="R49" s="8" t="inlineStr"/>
+      <c r="S49" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T49" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>WEEK TOTAL — 07/27/2026 - 08/02/2026</t>
         </is>
       </c>
-      <c r="B47" s="10" t="n"/>
-      <c r="C47" s="5" t="inlineStr"/>
-      <c r="D47" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E47" s="5" t="inlineStr"/>
-      <c r="F47" s="5" t="inlineStr"/>
-      <c r="G47" s="5" t="inlineStr"/>
-      <c r="H47" s="5" t="inlineStr"/>
-      <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="5" t="inlineStr"/>
-      <c r="K47" s="5" t="inlineStr"/>
-      <c r="L47" s="5" t="inlineStr"/>
-      <c r="M47" s="5" t="inlineStr"/>
-      <c r="N47" s="5" t="inlineStr"/>
-      <c r="O47" s="5" t="inlineStr"/>
-      <c r="P47" s="5" t="inlineStr"/>
-      <c r="Q47" s="5" t="inlineStr"/>
-      <c r="R47" s="5" t="inlineStr"/>
-      <c r="S47" s="5" t="inlineStr"/>
-      <c r="T47" s="5" t="n">
-        <v>2</v>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="5" t="inlineStr"/>
+      <c r="D50" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="N50" s="5" t="inlineStr"/>
+      <c r="O50" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="P50" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q50" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R50" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S50" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="T50" s="5" t="n">
+        <v>256</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A50:B50"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A47:B47"/>
@@ -2746,6 +2928,391 @@
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="A12:B12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Activity/General Notes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Completed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Scheduled</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Via Email</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Successful</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Unsuccessful</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call via Phone</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Phone Call</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Site Visit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Group Email</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Payment Delivery</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Incoming</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Outgoing</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>07/27/2026 - 08/02/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="N2" s="4" t="inlineStr"/>
+      <c r="O2" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="P2" s="4" t="inlineStr"/>
+      <c r="Q2" s="4" t="inlineStr"/>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="5" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>07/27/2026 - 08/02/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="inlineStr"/>
+      <c r="P3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="T3" s="5" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>07/27/2026 - 08/02/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>JR Scappini</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>07/27/2026 - 08/02/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="8" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 07/27/2026 - 08/02/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>256</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_activity.xlsx
+++ b/master_activity.xlsx
@@ -17,6 +17,7 @@
     <sheet name="Wk 07-13-2026" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Wk 07-20-2026" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Wk 07-27-2026" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Wk 08-03-2026" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Weeks'!$A$1:$T$1</definedName>
@@ -529,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T50"/>
+  <dimension ref="A1:T55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2728,11 +2729,7 @@
           <t>07/27/2026 - 08/02/2026</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Christine Mello</t>
-        </is>
-      </c>
+      <c r="B47" s="10" t="n"/>
       <c r="C47" s="8" t="inlineStr"/>
       <c r="D47" s="8" t="n">
         <v>6</v>
@@ -2910,9 +2907,254 @@
         <v>256</v>
       </c>
     </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>08/03/2026 - 08/09/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr"/>
+      <c r="D51" s="8" t="inlineStr"/>
+      <c r="E51" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F51" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G51" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H51" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K51" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="L51" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="M51" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="N51" s="8" t="inlineStr"/>
+      <c r="O51" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P51" s="8" t="inlineStr"/>
+      <c r="Q51" s="8" t="inlineStr"/>
+      <c r="R51" s="8" t="inlineStr"/>
+      <c r="S51" s="8" t="inlineStr"/>
+      <c r="T51" s="5" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>08/03/2026 - 08/09/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr"/>
+      <c r="D52" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" s="4" t="inlineStr"/>
+      <c r="G52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr"/>
+      <c r="K52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N52" s="4" t="inlineStr"/>
+      <c r="O52" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="P52" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R52" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T52" s="5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>08/03/2026 - 08/09/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr"/>
+      <c r="D53" s="8" t="inlineStr"/>
+      <c r="E53" s="8" t="inlineStr"/>
+      <c r="F53" s="8" t="inlineStr"/>
+      <c r="G53" s="8" t="inlineStr"/>
+      <c r="H53" s="8" t="inlineStr"/>
+      <c r="I53" s="8" t="inlineStr"/>
+      <c r="J53" s="8" t="inlineStr"/>
+      <c r="K53" s="8" t="inlineStr"/>
+      <c r="L53" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M53" s="8" t="inlineStr"/>
+      <c r="N53" s="8" t="inlineStr"/>
+      <c r="O53" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" s="8" t="inlineStr"/>
+      <c r="Q53" s="8" t="inlineStr"/>
+      <c r="R53" s="8" t="inlineStr"/>
+      <c r="S53" s="8" t="inlineStr"/>
+      <c r="T53" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>08/03/2026 - 08/09/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr"/>
+      <c r="D54" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
+      <c r="G54" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H54" s="4" t="inlineStr"/>
+      <c r="I54" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" s="4" t="inlineStr"/>
+      <c r="L54" s="4" t="inlineStr"/>
+      <c r="M54" s="4" t="inlineStr"/>
+      <c r="N54" s="4" t="inlineStr"/>
+      <c r="O54" s="4" t="inlineStr"/>
+      <c r="P54" s="4" t="inlineStr"/>
+      <c r="Q54" s="4" t="inlineStr"/>
+      <c r="R54" s="4" t="inlineStr"/>
+      <c r="S54" s="4" t="inlineStr"/>
+      <c r="T54" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 08/03/2026 - 08/09/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="5" t="inlineStr"/>
+      <c r="D55" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="M55" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="N55" s="5" t="inlineStr"/>
+      <c r="O55" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="P55" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q55" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R55" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="S55" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T55" s="5" t="n">
+        <v>123</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <mergeCells count="15">
+  <mergeCells count="16">
+    <mergeCell ref="A55:B55"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A15:B15"/>
@@ -3318,6 +3560,391 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Activity/General Notes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Completed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Scheduled</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Via Email</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Successful</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Unsuccessful</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call via Phone</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Phone Call</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Site Visit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Group Email</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Payment Delivery</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Incoming</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Outgoing</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>08/03/2026 - 08/09/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="N2" s="4" t="inlineStr"/>
+      <c r="O2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P2" s="4" t="inlineStr"/>
+      <c r="Q2" s="4" t="inlineStr"/>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
+      <c r="T2" s="5" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>08/03/2026 - 08/09/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="P3" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="S3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>08/03/2026 - 08/09/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>08/03/2026 - 08/09/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="8" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="inlineStr"/>
+      <c r="T5" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 08/03/2026 - 08/09/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>123</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:B6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/master_activity.xlsx
+++ b/master_activity.xlsx
@@ -18,6 +18,7 @@
     <sheet name="Wk 07-20-2026" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Wk 07-27-2026" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Wk 08-03-2026" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Wk 08-10-2026" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Weeks'!$A$1:$T$1</definedName>
@@ -530,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T55"/>
+  <dimension ref="A1:T60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3151,15 +3152,252 @@
         <v>123</v>
       </c>
     </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>08/10/2026 - 08/16/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr"/>
+      <c r="D56" s="4" t="inlineStr"/>
+      <c r="E56" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K56" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="L56" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="M56" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="N56" s="4" t="n">
+        <v>218</v>
+      </c>
+      <c r="O56" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P56" s="4" t="inlineStr"/>
+      <c r="Q56" s="4" t="inlineStr"/>
+      <c r="R56" s="4" t="inlineStr"/>
+      <c r="S56" s="4" t="inlineStr"/>
+      <c r="T56" s="5" t="n">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>08/10/2026 - 08/16/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr"/>
+      <c r="D57" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="8" t="inlineStr"/>
+      <c r="G57" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H57" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="I57" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J57" s="8" t="inlineStr"/>
+      <c r="K57" s="8" t="inlineStr"/>
+      <c r="L57" s="8" t="inlineStr"/>
+      <c r="M57" s="8" t="inlineStr"/>
+      <c r="N57" s="8" t="inlineStr"/>
+      <c r="O57" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="P57" s="8" t="inlineStr"/>
+      <c r="Q57" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R57" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S57" s="8" t="inlineStr"/>
+      <c r="T57" s="5" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>08/10/2026 - 08/16/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr"/>
+      <c r="D58" s="4" t="inlineStr"/>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr"/>
+      <c r="I58" s="4" t="inlineStr"/>
+      <c r="J58" s="4" t="inlineStr"/>
+      <c r="K58" s="4" t="inlineStr"/>
+      <c r="L58" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M58" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N58" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="O58" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P58" s="4" t="inlineStr"/>
+      <c r="Q58" s="4" t="inlineStr"/>
+      <c r="R58" s="4" t="inlineStr"/>
+      <c r="S58" s="4" t="inlineStr"/>
+      <c r="T58" s="5" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>08/10/2026 - 08/16/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr"/>
+      <c r="D59" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E59" s="8" t="inlineStr"/>
+      <c r="F59" s="8" t="inlineStr"/>
+      <c r="G59" s="8" t="inlineStr"/>
+      <c r="H59" s="8" t="inlineStr"/>
+      <c r="I59" s="8" t="inlineStr"/>
+      <c r="J59" s="8" t="inlineStr"/>
+      <c r="K59" s="8" t="inlineStr"/>
+      <c r="L59" s="8" t="inlineStr"/>
+      <c r="M59" s="8" t="inlineStr"/>
+      <c r="N59" s="8" t="inlineStr"/>
+      <c r="O59" s="8" t="inlineStr"/>
+      <c r="P59" s="8" t="inlineStr"/>
+      <c r="Q59" s="8" t="inlineStr"/>
+      <c r="R59" s="8" t="inlineStr"/>
+      <c r="S59" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T59" s="5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 08/10/2026 - 08/16/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="5" t="inlineStr"/>
+      <c r="D60" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="M60" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="N60" s="5" t="n">
+        <v>269</v>
+      </c>
+      <c r="O60" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="P60" s="5" t="inlineStr"/>
+      <c r="Q60" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R60" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S60" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T60" s="5" t="n">
+        <v>485</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A60:B60"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A47:B47"/>
@@ -3945,6 +4183,383 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Activity/General Notes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Completed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Scheduled</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Via Email</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Successful</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Unsuccessful</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call via Phone</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Phone Call</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Site Visit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Group Email</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Payment Delivery</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Incoming</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Outgoing</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>08/10/2026 - 08/16/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>218</v>
+      </c>
+      <c r="O2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P2" s="4" t="inlineStr"/>
+      <c r="Q2" s="4" t="inlineStr"/>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
+      <c r="T2" s="5" t="n">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>08/10/2026 - 08/16/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="8" t="inlineStr"/>
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="P3" s="8" t="inlineStr"/>
+      <c r="Q3" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" s="8" t="inlineStr"/>
+      <c r="T3" s="5" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>08/10/2026 - 08/16/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="5" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>08/10/2026 - 08/16/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="8" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 08/10/2026 - 08/16/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>269</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>485</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:B6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/master_activity.xlsx
+++ b/master_activity.xlsx
@@ -531,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T60"/>
+  <dimension ref="A1:T64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3166,31 +3166,31 @@
       <c r="C56" s="4" t="inlineStr"/>
       <c r="D56" s="4" t="inlineStr"/>
       <c r="E56" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J56" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F56" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G56" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="H56" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I56" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="J56" s="4" t="n">
-        <v>11</v>
-      </c>
       <c r="K56" s="4" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="L56" s="4" t="n">
         <v>11</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="N56" s="4" t="n">
         <v>218</v>
@@ -3203,7 +3203,7 @@
       <c r="R56" s="4" t="inlineStr"/>
       <c r="S56" s="4" t="inlineStr"/>
       <c r="T56" s="5" t="n">
-        <v>368</v>
+        <v>288</v>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
@@ -3278,20 +3278,16 @@
         <v>3</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="N58" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="O58" s="4" t="n">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N58" s="4" t="inlineStr"/>
+      <c r="O58" s="4" t="inlineStr"/>
       <c r="P58" s="4" t="inlineStr"/>
       <c r="Q58" s="4" t="inlineStr"/>
       <c r="R58" s="4" t="inlineStr"/>
       <c r="S58" s="4" t="inlineStr"/>
       <c r="T58" s="5" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1">
@@ -3324,10 +3320,10 @@
       <c r="Q59" s="8" t="inlineStr"/>
       <c r="R59" s="8" t="inlineStr"/>
       <c r="S59" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T59" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
@@ -3342,37 +3338,37 @@
         <v>11</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H60" s="5" t="n">
         <v>18</v>
       </c>
       <c r="I60" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K60" s="5" t="n">
         <v>15</v>
-      </c>
-      <c r="J60" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K60" s="5" t="n">
-        <v>34</v>
       </c>
       <c r="L60" s="5" t="n">
         <v>14</v>
       </c>
       <c r="M60" s="5" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="N60" s="5" t="n">
-        <v>269</v>
+        <v>218</v>
       </c>
       <c r="O60" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P60" s="5" t="inlineStr"/>
       <c r="Q60" s="5" t="n">
@@ -3382,22 +3378,187 @@
         <v>2</v>
       </c>
       <c r="S60" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T60" s="5" t="n">
-        <v>485</v>
+        <v>348</v>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr"/>
+      <c r="D61" s="8" t="inlineStr"/>
+      <c r="E61" s="8" t="inlineStr"/>
+      <c r="F61" s="8" t="inlineStr"/>
+      <c r="G61" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H61" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" s="8" t="inlineStr"/>
+      <c r="J61" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="L61" s="8" t="inlineStr"/>
+      <c r="M61" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="N61" s="8" t="inlineStr"/>
+      <c r="O61" s="8" t="inlineStr"/>
+      <c r="P61" s="8" t="inlineStr"/>
+      <c r="Q61" s="8" t="inlineStr"/>
+      <c r="R61" s="8" t="inlineStr"/>
+      <c r="S61" s="8" t="inlineStr"/>
+      <c r="T61" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr"/>
+      <c r="D62" s="4" t="inlineStr"/>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
+      <c r="H62" s="4" t="inlineStr"/>
+      <c r="I62" s="4" t="inlineStr"/>
+      <c r="J62" s="4" t="inlineStr"/>
+      <c r="K62" s="4" t="inlineStr"/>
+      <c r="L62" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M62" s="4" t="inlineStr"/>
+      <c r="N62" s="4" t="n">
+        <v>289</v>
+      </c>
+      <c r="O62" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P62" s="4" t="inlineStr"/>
+      <c r="Q62" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R62" s="4" t="inlineStr"/>
+      <c r="S62" s="4" t="inlineStr"/>
+      <c r="T62" s="5" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="n">
+        <v>191</v>
+      </c>
+      <c r="D63" s="8" t="inlineStr"/>
+      <c r="E63" s="8" t="inlineStr"/>
+      <c r="F63" s="8" t="inlineStr"/>
+      <c r="G63" s="8" t="inlineStr"/>
+      <c r="H63" s="8" t="inlineStr"/>
+      <c r="I63" s="8" t="inlineStr"/>
+      <c r="J63" s="8" t="inlineStr"/>
+      <c r="K63" s="8" t="inlineStr"/>
+      <c r="L63" s="8" t="inlineStr"/>
+      <c r="M63" s="8" t="inlineStr"/>
+      <c r="N63" s="8" t="inlineStr"/>
+      <c r="O63" s="8" t="inlineStr"/>
+      <c r="P63" s="8" t="inlineStr"/>
+      <c r="Q63" s="8" t="inlineStr"/>
+      <c r="R63" s="8" t="inlineStr"/>
+      <c r="S63" s="8" t="inlineStr"/>
+      <c r="T63" s="5" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="n"/>
+      <c r="C64" s="5" t="n">
+        <v>191</v>
+      </c>
+      <c r="D64" s="5" t="inlineStr"/>
+      <c r="E64" s="5" t="inlineStr"/>
+      <c r="F64" s="5" t="inlineStr"/>
+      <c r="G64" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" s="5" t="inlineStr"/>
+      <c r="J64" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M64" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="N64" s="5" t="n">
+        <v>289</v>
+      </c>
+      <c r="O64" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P64" s="5" t="inlineStr"/>
+      <c r="Q64" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R64" s="5" t="inlineStr"/>
+      <c r="S64" s="5" t="inlineStr"/>
+      <c r="T64" s="5" t="n">
+        <v>519</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <mergeCells count="17">
+  <mergeCells count="18">
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A60:B60"/>
     <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A60:B60"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A47:B47"/>
@@ -4189,7 +4350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4330,31 +4491,31 @@
       <c r="C2" s="4" t="inlineStr"/>
       <c r="D2" s="4" t="inlineStr"/>
       <c r="E2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J2" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F2" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>11</v>
-      </c>
       <c r="K2" s="4" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="L2" s="4" t="n">
         <v>11</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="N2" s="4" t="n">
         <v>218</v>
@@ -4367,7 +4528,7 @@
       <c r="R2" s="4" t="inlineStr"/>
       <c r="S2" s="4" t="inlineStr"/>
       <c r="T2" s="5" t="n">
-        <v>368</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -4442,20 +4603,16 @@
         <v>3</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr"/>
       <c r="P4" s="4" t="inlineStr"/>
       <c r="Q4" s="4" t="inlineStr"/>
       <c r="R4" s="4" t="inlineStr"/>
       <c r="S4" s="4" t="inlineStr"/>
       <c r="T4" s="5" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -4488,10 +4645,10 @@
       <c r="Q5" s="8" t="inlineStr"/>
       <c r="R5" s="8" t="inlineStr"/>
       <c r="S5" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -4506,37 +4663,37 @@
         <v>11</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>18</v>
       </c>
       <c r="I6" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" s="5" t="n">
         <v>15</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>34</v>
       </c>
       <c r="L6" s="5" t="n">
         <v>14</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>269</v>
+        <v>218</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="n">
@@ -4546,15 +4703,180 @@
         <v>2</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>485</v>
+        <v>348</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr"/>
+      <c r="D7" s="8" t="inlineStr"/>
+      <c r="E7" s="8" t="inlineStr"/>
+      <c r="F7" s="8" t="inlineStr"/>
+      <c r="G7" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="8" t="inlineStr"/>
+      <c r="J7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="L7" s="8" t="inlineStr"/>
+      <c r="M7" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="N7" s="8" t="inlineStr"/>
+      <c r="O7" s="8" t="inlineStr"/>
+      <c r="P7" s="8" t="inlineStr"/>
+      <c r="Q7" s="8" t="inlineStr"/>
+      <c r="R7" s="8" t="inlineStr"/>
+      <c r="S7" s="8" t="inlineStr"/>
+      <c r="T7" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" s="4" t="inlineStr"/>
+      <c r="N8" s="4" t="n">
+        <v>289</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr"/>
+      <c r="T8" s="5" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>191</v>
+      </c>
+      <c r="D9" s="8" t="inlineStr"/>
+      <c r="E9" s="8" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr"/>
+      <c r="G9" s="8" t="inlineStr"/>
+      <c r="H9" s="8" t="inlineStr"/>
+      <c r="I9" s="8" t="inlineStr"/>
+      <c r="J9" s="8" t="inlineStr"/>
+      <c r="K9" s="8" t="inlineStr"/>
+      <c r="L9" s="8" t="inlineStr"/>
+      <c r="M9" s="8" t="inlineStr"/>
+      <c r="N9" s="8" t="inlineStr"/>
+      <c r="O9" s="8" t="inlineStr"/>
+      <c r="P9" s="8" t="inlineStr"/>
+      <c r="Q9" s="8" t="inlineStr"/>
+      <c r="R9" s="8" t="inlineStr"/>
+      <c r="S9" s="8" t="inlineStr"/>
+      <c r="T9" s="5" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="5" t="n">
+        <v>191</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>289</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" s="5" t="inlineStr"/>
+      <c r="S10" s="5" t="inlineStr"/>
+      <c r="T10" s="5" t="n">
+        <v>519</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_activity.xlsx
+++ b/master_activity.xlsx
@@ -531,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T64"/>
+  <dimension ref="A1:T69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3153,274 +3153,264 @@
       </c>
     </row>
     <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr"/>
+      <c r="D56" s="8" t="inlineStr"/>
+      <c r="E56" s="8" t="inlineStr"/>
+      <c r="F56" s="8" t="inlineStr"/>
+      <c r="G56" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H56" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" s="8" t="inlineStr"/>
+      <c r="J56" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="L56" s="8" t="inlineStr"/>
+      <c r="M56" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="N56" s="8" t="inlineStr"/>
+      <c r="O56" s="8" t="inlineStr"/>
+      <c r="P56" s="8" t="inlineStr"/>
+      <c r="Q56" s="8" t="inlineStr"/>
+      <c r="R56" s="8" t="inlineStr"/>
+      <c r="S56" s="8" t="inlineStr"/>
+      <c r="T56" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr"/>
+      <c r="D57" s="4" t="inlineStr"/>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
+      <c r="G57" s="4" t="inlineStr"/>
+      <c r="H57" s="4" t="inlineStr"/>
+      <c r="I57" s="4" t="inlineStr"/>
+      <c r="J57" s="4" t="inlineStr"/>
+      <c r="K57" s="4" t="inlineStr"/>
+      <c r="L57" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M57" s="4" t="inlineStr"/>
+      <c r="N57" s="4" t="n">
+        <v>289</v>
+      </c>
+      <c r="O57" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P57" s="4" t="inlineStr"/>
+      <c r="Q57" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R57" s="4" t="inlineStr"/>
+      <c r="S57" s="4" t="inlineStr"/>
+      <c r="T57" s="5" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="n">
+        <v>191</v>
+      </c>
+      <c r="D58" s="8" t="inlineStr"/>
+      <c r="E58" s="8" t="inlineStr"/>
+      <c r="F58" s="8" t="inlineStr"/>
+      <c r="G58" s="8" t="inlineStr"/>
+      <c r="H58" s="8" t="inlineStr"/>
+      <c r="I58" s="8" t="inlineStr"/>
+      <c r="J58" s="8" t="inlineStr"/>
+      <c r="K58" s="8" t="inlineStr"/>
+      <c r="L58" s="8" t="inlineStr"/>
+      <c r="M58" s="8" t="inlineStr"/>
+      <c r="N58" s="8" t="inlineStr"/>
+      <c r="O58" s="8" t="inlineStr"/>
+      <c r="P58" s="8" t="inlineStr"/>
+      <c r="Q58" s="8" t="inlineStr"/>
+      <c r="R58" s="8" t="inlineStr"/>
+      <c r="S58" s="8" t="inlineStr"/>
+      <c r="T58" s="5" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="n"/>
+      <c r="C59" s="5" t="n">
+        <v>191</v>
+      </c>
+      <c r="D59" s="5" t="inlineStr"/>
+      <c r="E59" s="5" t="inlineStr"/>
+      <c r="F59" s="5" t="inlineStr"/>
+      <c r="G59" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" s="5" t="inlineStr"/>
+      <c r="J59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M59" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="N59" s="5" t="n">
+        <v>289</v>
+      </c>
+      <c r="O59" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P59" s="5" t="inlineStr"/>
+      <c r="Q59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R59" s="5" t="inlineStr"/>
+      <c r="S59" s="5" t="inlineStr"/>
+      <c r="T59" s="5" t="n">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>08/10/2026 - 08/16/2026</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>Carlos Casillas</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr"/>
-      <c r="D56" s="4" t="inlineStr"/>
-      <c r="E56" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F56" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G56" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="H56" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I56" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="J56" s="4" t="n">
+      <c r="C60" s="4" t="inlineStr"/>
+      <c r="D60" s="4" t="inlineStr"/>
+      <c r="E60" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H60" s="4" t="inlineStr"/>
+      <c r="I60" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="K56" s="4" t="n">
+      <c r="J60" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K60" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="L56" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="M56" s="4" t="n">
+      <c r="L60" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M60" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="N56" s="4" t="n">
+      <c r="N60" s="4" t="n">
         <v>218</v>
       </c>
-      <c r="O56" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="P56" s="4" t="inlineStr"/>
-      <c r="Q56" s="4" t="inlineStr"/>
-      <c r="R56" s="4" t="inlineStr"/>
-      <c r="S56" s="4" t="inlineStr"/>
-      <c r="T56" s="5" t="n">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>08/10/2026 - 08/16/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>Christine Mello</t>
-        </is>
-      </c>
-      <c r="C57" s="8" t="inlineStr"/>
-      <c r="D57" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E57" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F57" s="8" t="inlineStr"/>
-      <c r="G57" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H57" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="I57" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="J57" s="8" t="inlineStr"/>
-      <c r="K57" s="8" t="inlineStr"/>
-      <c r="L57" s="8" t="inlineStr"/>
-      <c r="M57" s="8" t="inlineStr"/>
-      <c r="N57" s="8" t="inlineStr"/>
-      <c r="O57" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="P57" s="8" t="inlineStr"/>
-      <c r="Q57" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="R57" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S57" s="8" t="inlineStr"/>
-      <c r="T57" s="5" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>08/10/2026 - 08/16/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>Michael Petrick</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr"/>
-      <c r="D58" s="4" t="inlineStr"/>
-      <c r="E58" s="4" t="inlineStr"/>
-      <c r="F58" s="4" t="inlineStr"/>
-      <c r="G58" s="4" t="inlineStr"/>
-      <c r="H58" s="4" t="inlineStr"/>
-      <c r="I58" s="4" t="inlineStr"/>
-      <c r="J58" s="4" t="inlineStr"/>
-      <c r="K58" s="4" t="inlineStr"/>
-      <c r="L58" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M58" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N58" s="4" t="inlineStr"/>
-      <c r="O58" s="4" t="inlineStr"/>
-      <c r="P58" s="4" t="inlineStr"/>
-      <c r="Q58" s="4" t="inlineStr"/>
-      <c r="R58" s="4" t="inlineStr"/>
-      <c r="S58" s="4" t="inlineStr"/>
-      <c r="T58" s="5" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>08/10/2026 - 08/16/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>Roger Guzowski</t>
-        </is>
-      </c>
-      <c r="C59" s="8" t="inlineStr"/>
-      <c r="D59" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="E59" s="8" t="inlineStr"/>
-      <c r="F59" s="8" t="inlineStr"/>
-      <c r="G59" s="8" t="inlineStr"/>
-      <c r="H59" s="8" t="inlineStr"/>
-      <c r="I59" s="8" t="inlineStr"/>
-      <c r="J59" s="8" t="inlineStr"/>
-      <c r="K59" s="8" t="inlineStr"/>
-      <c r="L59" s="8" t="inlineStr"/>
-      <c r="M59" s="8" t="inlineStr"/>
-      <c r="N59" s="8" t="inlineStr"/>
-      <c r="O59" s="8" t="inlineStr"/>
-      <c r="P59" s="8" t="inlineStr"/>
-      <c r="Q59" s="8" t="inlineStr"/>
-      <c r="R59" s="8" t="inlineStr"/>
-      <c r="S59" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T59" s="5" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="9" t="inlineStr">
-        <is>
-          <t>WEEK TOTAL — 08/10/2026 - 08/16/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="10" t="n"/>
-      <c r="C60" s="5" t="inlineStr"/>
-      <c r="D60" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="E60" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F60" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="H60" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="I60" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="J60" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="K60" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="L60" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="M60" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="N60" s="5" t="n">
-        <v>218</v>
-      </c>
-      <c r="O60" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="P60" s="5" t="inlineStr"/>
-      <c r="Q60" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="R60" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S60" s="5" t="n">
-        <v>2</v>
-      </c>
+      <c r="O60" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P60" s="4" t="inlineStr"/>
+      <c r="Q60" s="4" t="inlineStr"/>
+      <c r="R60" s="4" t="inlineStr"/>
+      <c r="S60" s="4" t="inlineStr"/>
       <c r="T60" s="5" t="n">
-        <v>348</v>
+        <v>281</v>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>08/17/2026 - 08/23/2026</t>
+          <t>08/10/2026 - 08/16/2026</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>Carlos Casillas</t>
+          <t>Christine Mello</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr"/>
-      <c r="D61" s="8" t="inlineStr"/>
-      <c r="E61" s="8" t="inlineStr"/>
+      <c r="D61" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="F61" s="8" t="inlineStr"/>
       <c r="G61" s="8" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I61" s="8" t="inlineStr"/>
-      <c r="J61" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K61" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="I61" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J61" s="8" t="inlineStr"/>
+      <c r="K61" s="8" t="inlineStr"/>
+      <c r="L61" s="8" t="inlineStr"/>
+      <c r="M61" s="8" t="inlineStr"/>
+      <c r="N61" s="8" t="inlineStr"/>
+      <c r="O61" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="L61" s="8" t="inlineStr"/>
-      <c r="M61" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="N61" s="8" t="inlineStr"/>
-      <c r="O61" s="8" t="inlineStr"/>
       <c r="P61" s="8" t="inlineStr"/>
-      <c r="Q61" s="8" t="inlineStr"/>
-      <c r="R61" s="8" t="inlineStr"/>
+      <c r="Q61" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R61" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="S61" s="8" t="inlineStr"/>
       <c r="T61" s="5" t="n">
         <v>34</v>
@@ -3429,7 +3419,7 @@
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>08/17/2026 - 08/23/2026</t>
+          <t>08/10/2026 - 08/16/2026</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -3449,27 +3439,23 @@
       <c r="L62" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M62" s="4" t="inlineStr"/>
-      <c r="N62" s="4" t="n">
-        <v>289</v>
-      </c>
-      <c r="O62" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="M62" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" s="4" t="inlineStr"/>
+      <c r="O62" s="4" t="inlineStr"/>
       <c r="P62" s="4" t="inlineStr"/>
-      <c r="Q62" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q62" s="4" t="inlineStr"/>
       <c r="R62" s="4" t="inlineStr"/>
       <c r="S62" s="4" t="inlineStr"/>
       <c r="T62" s="5" t="n">
-        <v>294</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>08/17/2026 - 08/23/2026</t>
+          <t>08/10/2026 - 08/16/2026</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
@@ -3477,10 +3463,10 @@
           <t>Roger Guzowski</t>
         </is>
       </c>
-      <c r="C63" s="8" t="n">
-        <v>191</v>
-      </c>
-      <c r="D63" s="8" t="inlineStr"/>
+      <c r="C63" s="8" t="inlineStr"/>
+      <c r="D63" s="8" t="n">
+        <v>9</v>
+      </c>
       <c r="E63" s="8" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr"/>
       <c r="G63" s="8" t="inlineStr"/>
@@ -3495,80 +3481,309 @@
       <c r="P63" s="8" t="inlineStr"/>
       <c r="Q63" s="8" t="inlineStr"/>
       <c r="R63" s="8" t="inlineStr"/>
-      <c r="S63" s="8" t="inlineStr"/>
+      <c r="S63" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="T63" s="5" t="n">
-        <v>191</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>WEEK TOTAL — 08/17/2026 - 08/23/2026</t>
+          <t>WEEK TOTAL — 08/10/2026 - 08/16/2026</t>
         </is>
       </c>
       <c r="B64" s="10" t="n"/>
-      <c r="C64" s="5" t="n">
-        <v>191</v>
-      </c>
-      <c r="D64" s="5" t="inlineStr"/>
-      <c r="E64" s="5" t="inlineStr"/>
-      <c r="F64" s="5" t="inlineStr"/>
+      <c r="C64" s="5" t="inlineStr"/>
+      <c r="D64" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="G64" s="5" t="n">
         <v>13</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I64" s="5" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>9</v>
+      </c>
       <c r="J64" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M64" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N64" s="5" t="n">
-        <v>289</v>
+        <v>218</v>
       </c>
       <c r="O64" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="P64" s="5" t="inlineStr"/>
       <c r="Q64" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R64" s="5" t="inlineStr"/>
-      <c r="S64" s="5" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="R64" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S64" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="T64" s="5" t="n">
-        <v>519</v>
+        <v>329</v>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr"/>
+      <c r="D65" s="8" t="inlineStr"/>
+      <c r="E65" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F65" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G65" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H65" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" s="8" t="inlineStr"/>
+      <c r="J65" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K65" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="L65" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M65" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="N65" s="8" t="inlineStr"/>
+      <c r="O65" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P65" s="8" t="inlineStr"/>
+      <c r="Q65" s="8" t="inlineStr"/>
+      <c r="R65" s="8" t="inlineStr"/>
+      <c r="S65" s="8" t="inlineStr"/>
+      <c r="T65" s="5" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr"/>
+      <c r="D66" s="4" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
+      <c r="G66" s="4" t="inlineStr"/>
+      <c r="H66" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I66" s="4" t="inlineStr"/>
+      <c r="J66" s="4" t="inlineStr"/>
+      <c r="K66" s="4" t="inlineStr"/>
+      <c r="L66" s="4" t="inlineStr"/>
+      <c r="M66" s="4" t="inlineStr"/>
+      <c r="N66" s="4" t="inlineStr"/>
+      <c r="O66" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P66" s="4" t="inlineStr"/>
+      <c r="Q66" s="4" t="inlineStr"/>
+      <c r="R66" s="4" t="inlineStr"/>
+      <c r="S66" s="4" t="inlineStr"/>
+      <c r="T66" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr"/>
+      <c r="D67" s="8" t="inlineStr"/>
+      <c r="E67" s="8" t="inlineStr"/>
+      <c r="F67" s="8" t="inlineStr"/>
+      <c r="G67" s="8" t="inlineStr"/>
+      <c r="H67" s="8" t="inlineStr"/>
+      <c r="I67" s="8" t="inlineStr"/>
+      <c r="J67" s="8" t="inlineStr"/>
+      <c r="K67" s="8" t="inlineStr"/>
+      <c r="L67" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M67" s="8" t="inlineStr"/>
+      <c r="N67" s="8" t="n">
+        <v>289</v>
+      </c>
+      <c r="O67" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P67" s="8" t="inlineStr"/>
+      <c r="Q67" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R67" s="8" t="inlineStr"/>
+      <c r="S67" s="8" t="inlineStr"/>
+      <c r="T67" s="5" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>191</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
+      <c r="G68" s="4" t="inlineStr"/>
+      <c r="H68" s="4" t="inlineStr"/>
+      <c r="I68" s="4" t="inlineStr"/>
+      <c r="J68" s="4" t="inlineStr"/>
+      <c r="K68" s="4" t="inlineStr"/>
+      <c r="L68" s="4" t="inlineStr"/>
+      <c r="M68" s="4" t="inlineStr"/>
+      <c r="N68" s="4" t="inlineStr"/>
+      <c r="O68" s="4" t="inlineStr"/>
+      <c r="P68" s="4" t="inlineStr"/>
+      <c r="Q68" s="4" t="inlineStr"/>
+      <c r="R68" s="4" t="inlineStr"/>
+      <c r="S68" s="4" t="inlineStr"/>
+      <c r="T68" s="5" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="n"/>
+      <c r="C69" s="5" t="n">
+        <v>191</v>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I69" s="5" t="inlineStr"/>
+      <c r="J69" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M69" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="N69" s="5" t="n">
+        <v>289</v>
+      </c>
+      <c r="O69" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="P69" s="5" t="inlineStr"/>
+      <c r="Q69" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R69" s="5" t="inlineStr"/>
+      <c r="S69" s="5" t="inlineStr"/>
+      <c r="T69" s="5" t="n">
+        <v>565</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <mergeCells count="18">
-    <mergeCell ref="A55:B55"/>
+  <mergeCells count="19">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A7:B7"/>
     <mergeCell ref="A64:B64"/>
     <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A10:B10"/>
     <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A47:B47"/>
     <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A7:B7"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A47:B47"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A39:B39"/>
     <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4350,7 +4565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4497,22 +4712,20 @@
         <v>3</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="H2" s="4" t="inlineStr"/>
       <c r="I2" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>15</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M2" s="4" t="n">
         <v>13</v>
@@ -4528,7 +4741,7 @@
       <c r="R2" s="4" t="inlineStr"/>
       <c r="S2" s="4" t="inlineStr"/>
       <c r="T2" s="5" t="n">
-        <v>288</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -4554,10 +4767,10 @@
         <v>3</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I3" s="8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J3" s="8" t="inlineStr"/>
       <c r="K3" s="8" t="inlineStr"/>
@@ -4576,7 +4789,7 @@
       </c>
       <c r="S3" s="8" t="inlineStr"/>
       <c r="T3" s="5" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -4600,10 +4813,10 @@
       <c r="J4" s="4" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr"/>
       <c r="L4" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N4" s="4" t="inlineStr"/>
       <c r="O4" s="4" t="inlineStr"/>
@@ -4612,7 +4825,7 @@
       <c r="R4" s="4" t="inlineStr"/>
       <c r="S4" s="4" t="inlineStr"/>
       <c r="T4" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -4669,25 +4882,25 @@
         <v>3</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K6" s="5" t="n">
         <v>15</v>
       </c>
       <c r="L6" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M6" s="5" t="n">
         <v>14</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>15</v>
       </c>
       <c r="N6" s="5" t="n">
         <v>218</v>
@@ -4706,7 +4919,7 @@
         <v>2</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>348</v>
+        <v>329</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -4722,33 +4935,41 @@
       </c>
       <c r="C7" s="8" t="inlineStr"/>
       <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
+      <c r="E7" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="G7" s="8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H7" s="8" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="8" t="inlineStr"/>
       <c r="J7" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="L7" s="8" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="M7" s="8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N7" s="8" t="inlineStr"/>
-      <c r="O7" s="8" t="inlineStr"/>
+      <c r="O7" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="P7" s="8" t="inlineStr"/>
       <c r="Q7" s="8" t="inlineStr"/>
       <c r="R7" s="8" t="inlineStr"/>
       <c r="S7" s="8" t="inlineStr"/>
       <c r="T7" s="5" t="n">
-        <v>34</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -4759,7 +4980,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Michael Petrick</t>
+          <t>Christine Mello</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -4767,28 +4988,24 @@
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="I8" s="4" t="inlineStr"/>
       <c r="J8" s="4" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="L8" s="4" t="inlineStr"/>
       <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="n">
-        <v>289</v>
-      </c>
+      <c r="N8" s="4" t="inlineStr"/>
       <c r="O8" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q8" s="4" t="inlineStr"/>
       <c r="R8" s="4" t="inlineStr"/>
       <c r="S8" s="4" t="inlineStr"/>
       <c r="T8" s="5" t="n">
-        <v>294</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -4799,12 +5016,10 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Roger Guzowski</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>191</v>
-      </c>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr"/>
       <c r="D9" s="8" t="inlineStr"/>
       <c r="E9" s="8" t="inlineStr"/>
       <c r="F9" s="8" t="inlineStr"/>
@@ -4813,70 +5028,120 @@
       <c r="I9" s="8" t="inlineStr"/>
       <c r="J9" s="8" t="inlineStr"/>
       <c r="K9" s="8" t="inlineStr"/>
-      <c r="L9" s="8" t="inlineStr"/>
+      <c r="L9" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="M9" s="8" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
-      <c r="O9" s="8" t="inlineStr"/>
+      <c r="N9" s="8" t="n">
+        <v>289</v>
+      </c>
+      <c r="O9" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="P9" s="8" t="inlineStr"/>
-      <c r="Q9" s="8" t="inlineStr"/>
+      <c r="Q9" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="R9" s="8" t="inlineStr"/>
       <c r="S9" s="8" t="inlineStr"/>
       <c r="T9" s="5" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
         <v>191</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="D10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr"/>
+      <c r="L10" s="4" t="inlineStr"/>
+      <c r="M10" s="4" t="inlineStr"/>
+      <c r="N10" s="4" t="inlineStr"/>
+      <c r="O10" s="4" t="inlineStr"/>
+      <c r="P10" s="4" t="inlineStr"/>
+      <c r="Q10" s="4" t="inlineStr"/>
+      <c r="R10" s="4" t="inlineStr"/>
+      <c r="S10" s="4" t="inlineStr"/>
+      <c r="T10" s="5" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>WEEK TOTAL — 08/17/2026 - 08/23/2026</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="5" t="n">
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="5" t="n">
         <v>191</v>
       </c>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="5" t="n">
+      <c r="D11" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="L10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="N10" s="5" t="n">
+      <c r="F11" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="N11" s="5" t="n">
         <v>289</v>
       </c>
-      <c r="O10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="P10" s="5" t="inlineStr"/>
-      <c r="Q10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" s="5" t="inlineStr"/>
-      <c r="S10" s="5" t="inlineStr"/>
-      <c r="T10" s="5" t="n">
-        <v>519</v>
+      <c r="O11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" s="5" t="inlineStr"/>
+      <c r="S11" s="5" t="inlineStr"/>
+      <c r="T11" s="5" t="n">
+        <v>565</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A10:B10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_activity.xlsx
+++ b/master_activity.xlsx
@@ -531,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T69"/>
+  <dimension ref="A1:T74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3317,239 +3317,225 @@
       </c>
     </row>
     <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>08/10/2026 - 08/16/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>Carlos Casillas</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr"/>
-      <c r="D60" s="4" t="inlineStr"/>
-      <c r="E60" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F60" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G60" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H60" s="4" t="inlineStr"/>
-      <c r="I60" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J60" s="4" t="n">
+      <c r="C60" s="8" t="inlineStr"/>
+      <c r="D60" s="8" t="inlineStr"/>
+      <c r="E60" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F60" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="K60" s="4" t="n">
+      <c r="G60" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H60" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" s="8" t="inlineStr"/>
+      <c r="J60" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K60" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="L60" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="M60" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="N60" s="4" t="n">
-        <v>218</v>
-      </c>
-      <c r="O60" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="P60" s="4" t="inlineStr"/>
-      <c r="Q60" s="4" t="inlineStr"/>
-      <c r="R60" s="4" t="inlineStr"/>
-      <c r="S60" s="4" t="inlineStr"/>
+      <c r="L60" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M60" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="N60" s="8" t="inlineStr"/>
+      <c r="O60" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P60" s="8" t="inlineStr"/>
+      <c r="Q60" s="8" t="inlineStr"/>
+      <c r="R60" s="8" t="inlineStr"/>
+      <c r="S60" s="8" t="inlineStr"/>
       <c r="T60" s="5" t="n">
-        <v>281</v>
+        <v>69</v>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>08/10/2026 - 08/16/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>Christine Mello</t>
         </is>
       </c>
-      <c r="C61" s="8" t="inlineStr"/>
-      <c r="D61" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E61" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F61" s="8" t="inlineStr"/>
-      <c r="G61" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H61" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="I61" s="8" t="n">
+      <c r="C61" s="4" t="inlineStr"/>
+      <c r="D61" s="4" t="inlineStr"/>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr"/>
+      <c r="H61" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="J61" s="8" t="inlineStr"/>
-      <c r="K61" s="8" t="inlineStr"/>
-      <c r="L61" s="8" t="inlineStr"/>
-      <c r="M61" s="8" t="inlineStr"/>
-      <c r="N61" s="8" t="inlineStr"/>
-      <c r="O61" s="8" t="n">
+      <c r="I61" s="4" t="inlineStr"/>
+      <c r="J61" s="4" t="inlineStr"/>
+      <c r="K61" s="4" t="inlineStr"/>
+      <c r="L61" s="4" t="inlineStr"/>
+      <c r="M61" s="4" t="inlineStr"/>
+      <c r="N61" s="4" t="inlineStr"/>
+      <c r="O61" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P61" s="4" t="inlineStr"/>
+      <c r="Q61" s="4" t="inlineStr"/>
+      <c r="R61" s="4" t="inlineStr"/>
+      <c r="S61" s="4" t="inlineStr"/>
+      <c r="T61" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="P61" s="8" t="inlineStr"/>
-      <c r="Q61" s="8" t="n">
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr"/>
+      <c r="D62" s="8" t="inlineStr"/>
+      <c r="E62" s="8" t="inlineStr"/>
+      <c r="F62" s="8" t="inlineStr"/>
+      <c r="G62" s="8" t="inlineStr"/>
+      <c r="H62" s="8" t="inlineStr"/>
+      <c r="I62" s="8" t="inlineStr"/>
+      <c r="J62" s="8" t="inlineStr"/>
+      <c r="K62" s="8" t="inlineStr"/>
+      <c r="L62" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M62" s="8" t="inlineStr"/>
+      <c r="N62" s="8" t="n">
+        <v>289</v>
+      </c>
+      <c r="O62" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P62" s="8" t="inlineStr"/>
+      <c r="Q62" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R62" s="8" t="inlineStr"/>
+      <c r="S62" s="8" t="inlineStr"/>
+      <c r="T62" s="5" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>191</v>
+      </c>
+      <c r="D63" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="R61" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S61" s="8" t="inlineStr"/>
-      <c r="T61" s="5" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>08/10/2026 - 08/16/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>Michael Petrick</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr"/>
-      <c r="D62" s="4" t="inlineStr"/>
-      <c r="E62" s="4" t="inlineStr"/>
-      <c r="F62" s="4" t="inlineStr"/>
-      <c r="G62" s="4" t="inlineStr"/>
-      <c r="H62" s="4" t="inlineStr"/>
-      <c r="I62" s="4" t="inlineStr"/>
-      <c r="J62" s="4" t="inlineStr"/>
-      <c r="K62" s="4" t="inlineStr"/>
-      <c r="L62" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M62" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N62" s="4" t="inlineStr"/>
-      <c r="O62" s="4" t="inlineStr"/>
-      <c r="P62" s="4" t="inlineStr"/>
-      <c r="Q62" s="4" t="inlineStr"/>
-      <c r="R62" s="4" t="inlineStr"/>
-      <c r="S62" s="4" t="inlineStr"/>
-      <c r="T62" s="5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>08/10/2026 - 08/16/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>Roger Guzowski</t>
-        </is>
-      </c>
-      <c r="C63" s="8" t="inlineStr"/>
-      <c r="D63" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="E63" s="8" t="inlineStr"/>
-      <c r="F63" s="8" t="inlineStr"/>
-      <c r="G63" s="8" t="inlineStr"/>
-      <c r="H63" s="8" t="inlineStr"/>
-      <c r="I63" s="8" t="inlineStr"/>
-      <c r="J63" s="8" t="inlineStr"/>
-      <c r="K63" s="8" t="inlineStr"/>
-      <c r="L63" s="8" t="inlineStr"/>
-      <c r="M63" s="8" t="inlineStr"/>
-      <c r="N63" s="8" t="inlineStr"/>
-      <c r="O63" s="8" t="inlineStr"/>
-      <c r="P63" s="8" t="inlineStr"/>
-      <c r="Q63" s="8" t="inlineStr"/>
-      <c r="R63" s="8" t="inlineStr"/>
-      <c r="S63" s="8" t="n">
-        <v>2</v>
-      </c>
+      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="inlineStr"/>
+      <c r="G63" s="4" t="inlineStr"/>
+      <c r="H63" s="4" t="inlineStr"/>
+      <c r="I63" s="4" t="inlineStr"/>
+      <c r="J63" s="4" t="inlineStr"/>
+      <c r="K63" s="4" t="inlineStr"/>
+      <c r="L63" s="4" t="inlineStr"/>
+      <c r="M63" s="4" t="inlineStr"/>
+      <c r="N63" s="4" t="inlineStr"/>
+      <c r="O63" s="4" t="inlineStr"/>
+      <c r="P63" s="4" t="inlineStr"/>
+      <c r="Q63" s="4" t="inlineStr"/>
+      <c r="R63" s="4" t="inlineStr"/>
+      <c r="S63" s="4" t="inlineStr"/>
       <c r="T63" s="5" t="n">
-        <v>11</v>
+        <v>195</v>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>WEEK TOTAL — 08/10/2026 - 08/16/2026</t>
+          <t>WEEK TOTAL — 08/17/2026 - 08/23/2026</t>
         </is>
       </c>
       <c r="B64" s="10" t="n"/>
-      <c r="C64" s="5" t="inlineStr"/>
+      <c r="C64" s="5" t="n">
+        <v>191</v>
+      </c>
       <c r="D64" s="5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E64" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F64" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F64" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="G64" s="5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="I64" s="5" t="n">
-        <v>9</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="I64" s="5" t="inlineStr"/>
       <c r="J64" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K64" s="5" t="n">
         <v>15</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M64" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N64" s="5" t="n">
-        <v>218</v>
+        <v>289</v>
       </c>
       <c r="O64" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P64" s="5" t="inlineStr"/>
       <c r="Q64" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="R64" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S64" s="5" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="R64" s="5" t="inlineStr"/>
+      <c r="S64" s="5" t="inlineStr"/>
       <c r="T64" s="5" t="n">
-        <v>329</v>
+        <v>565</v>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>08/17/2026 - 08/23/2026</t>
+          <t>08/10/2026 - 08/16/2026</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
@@ -3560,31 +3546,33 @@
       <c r="C65" s="8" t="inlineStr"/>
       <c r="D65" s="8" t="inlineStr"/>
       <c r="E65" s="8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F65" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G65" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H65" s="8" t="inlineStr"/>
+      <c r="I65" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J65" s="8" t="n">
         <v>4</v>
-      </c>
-      <c r="G65" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="H65" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I65" s="8" t="inlineStr"/>
-      <c r="J65" s="8" t="n">
-        <v>6</v>
       </c>
       <c r="K65" s="8" t="n">
         <v>15</v>
       </c>
       <c r="L65" s="8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M65" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="N65" s="8" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="N65" s="8" t="n">
+        <v>218</v>
+      </c>
       <c r="O65" s="8" t="n">
         <v>2</v>
       </c>
@@ -3593,13 +3581,13 @@
       <c r="R65" s="8" t="inlineStr"/>
       <c r="S65" s="8" t="inlineStr"/>
       <c r="T65" s="5" t="n">
-        <v>69</v>
+        <v>281</v>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>08/17/2026 - 08/23/2026</t>
+          <t>08/10/2026 - 08/16/2026</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -3608,34 +3596,46 @@
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr"/>
-      <c r="D66" s="4" t="inlineStr"/>
-      <c r="E66" s="4" t="inlineStr"/>
+      <c r="D66" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="F66" s="4" t="inlineStr"/>
-      <c r="G66" s="4" t="inlineStr"/>
+      <c r="G66" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="H66" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I66" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I66" s="4" t="inlineStr"/>
       <c r="J66" s="4" t="inlineStr"/>
       <c r="K66" s="4" t="inlineStr"/>
       <c r="L66" s="4" t="inlineStr"/>
       <c r="M66" s="4" t="inlineStr"/>
       <c r="N66" s="4" t="inlineStr"/>
       <c r="O66" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P66" s="4" t="inlineStr"/>
-      <c r="Q66" s="4" t="inlineStr"/>
-      <c r="R66" s="4" t="inlineStr"/>
+      <c r="Q66" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R66" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="S66" s="4" t="inlineStr"/>
       <c r="T66" s="5" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>08/17/2026 - 08/23/2026</t>
+          <t>08/10/2026 - 08/16/2026</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
@@ -3655,27 +3655,23 @@
       <c r="L67" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="M67" s="8" t="inlineStr"/>
-      <c r="N67" s="8" t="n">
-        <v>289</v>
-      </c>
-      <c r="O67" s="8" t="n">
-        <v>2</v>
-      </c>
+      <c r="M67" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N67" s="8" t="inlineStr"/>
+      <c r="O67" s="8" t="inlineStr"/>
       <c r="P67" s="8" t="inlineStr"/>
-      <c r="Q67" s="8" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q67" s="8" t="inlineStr"/>
       <c r="R67" s="8" t="inlineStr"/>
       <c r="S67" s="8" t="inlineStr"/>
       <c r="T67" s="5" t="n">
-        <v>294</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>08/17/2026 - 08/23/2026</t>
+          <t>08/10/2026 - 08/16/2026</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -3683,11 +3679,9 @@
           <t>Roger Guzowski</t>
         </is>
       </c>
-      <c r="C68" s="4" t="n">
-        <v>191</v>
-      </c>
+      <c r="C68" s="4" t="inlineStr"/>
       <c r="D68" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E68" s="4" t="inlineStr"/>
       <c r="F68" s="4" t="inlineStr"/>
@@ -3703,68 +3697,294 @@
       <c r="P68" s="4" t="inlineStr"/>
       <c r="Q68" s="4" t="inlineStr"/>
       <c r="R68" s="4" t="inlineStr"/>
-      <c r="S68" s="4" t="inlineStr"/>
+      <c r="S68" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="T68" s="5" t="n">
-        <v>195</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>WEEK TOTAL — 08/17/2026 - 08/23/2026</t>
+          <t>WEEK TOTAL — 08/10/2026 - 08/16/2026</t>
         </is>
       </c>
       <c r="B69" s="10" t="n"/>
-      <c r="C69" s="5" t="n">
-        <v>191</v>
-      </c>
+      <c r="C69" s="5" t="inlineStr"/>
       <c r="D69" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E69" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E69" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="F69" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J69" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="G69" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="H69" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I69" s="5" t="inlineStr"/>
-      <c r="J69" s="5" t="n">
-        <v>6</v>
       </c>
       <c r="K69" s="5" t="n">
         <v>15</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N69" s="5" t="n">
-        <v>289</v>
+        <v>218</v>
       </c>
       <c r="O69" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P69" s="5" t="inlineStr"/>
       <c r="Q69" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R69" s="5" t="inlineStr"/>
-      <c r="S69" s="5" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="R69" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S69" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="T69" s="5" t="n">
-        <v>565</v>
+        <v>329</v>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr"/>
+      <c r="D70" s="4" t="inlineStr"/>
+      <c r="E70" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" s="4" t="inlineStr"/>
+      <c r="J70" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K70" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L70" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M70" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="N70" s="4" t="inlineStr"/>
+      <c r="O70" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P70" s="4" t="inlineStr"/>
+      <c r="Q70" s="4" t="inlineStr"/>
+      <c r="R70" s="4" t="inlineStr"/>
+      <c r="S70" s="4" t="inlineStr"/>
+      <c r="T70" s="5" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr"/>
+      <c r="D71" s="8" t="inlineStr"/>
+      <c r="E71" s="8" t="inlineStr"/>
+      <c r="F71" s="8" t="inlineStr"/>
+      <c r="G71" s="8" t="inlineStr"/>
+      <c r="H71" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I71" s="8" t="inlineStr"/>
+      <c r="J71" s="8" t="inlineStr"/>
+      <c r="K71" s="8" t="inlineStr"/>
+      <c r="L71" s="8" t="inlineStr"/>
+      <c r="M71" s="8" t="inlineStr"/>
+      <c r="N71" s="8" t="inlineStr"/>
+      <c r="O71" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P71" s="8" t="inlineStr"/>
+      <c r="Q71" s="8" t="inlineStr"/>
+      <c r="R71" s="8" t="inlineStr"/>
+      <c r="S71" s="8" t="inlineStr"/>
+      <c r="T71" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr"/>
+      <c r="D72" s="4" t="inlineStr"/>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr"/>
+      <c r="H72" s="4" t="inlineStr"/>
+      <c r="I72" s="4" t="inlineStr"/>
+      <c r="J72" s="4" t="inlineStr"/>
+      <c r="K72" s="4" t="inlineStr"/>
+      <c r="L72" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M72" s="4" t="inlineStr"/>
+      <c r="N72" s="4" t="n">
+        <v>289</v>
+      </c>
+      <c r="O72" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P72" s="4" t="inlineStr"/>
+      <c r="Q72" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R72" s="4" t="inlineStr"/>
+      <c r="S72" s="4" t="inlineStr"/>
+      <c r="T72" s="5" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="n">
+        <v>191</v>
+      </c>
+      <c r="D73" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E73" s="8" t="inlineStr"/>
+      <c r="F73" s="8" t="inlineStr"/>
+      <c r="G73" s="8" t="inlineStr"/>
+      <c r="H73" s="8" t="inlineStr"/>
+      <c r="I73" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" s="8" t="inlineStr"/>
+      <c r="K73" s="8" t="inlineStr"/>
+      <c r="L73" s="8" t="inlineStr"/>
+      <c r="M73" s="8" t="inlineStr"/>
+      <c r="N73" s="8" t="inlineStr"/>
+      <c r="O73" s="8" t="inlineStr"/>
+      <c r="P73" s="8" t="inlineStr"/>
+      <c r="Q73" s="8" t="inlineStr"/>
+      <c r="R73" s="8" t="inlineStr"/>
+      <c r="S73" s="8" t="inlineStr"/>
+      <c r="T73" s="5" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="n"/>
+      <c r="C74" s="5" t="n">
+        <v>191</v>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M74" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="N74" s="5" t="n">
+        <v>289</v>
+      </c>
+      <c r="O74" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="P74" s="5" t="inlineStr"/>
+      <c r="Q74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R74" s="5" t="inlineStr"/>
+      <c r="S74" s="5" t="inlineStr"/>
+      <c r="T74" s="5" t="n">
+        <v>566</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A15:B15"/>
@@ -3774,6 +3994,7 @@
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A69:B69"/>
     <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A74:B74"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A55:B55"/>
@@ -5069,7 +5290,9 @@
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="J10" s="4" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr"/>
       <c r="L10" s="4" t="inlineStr"/>
@@ -5081,7 +5304,7 @@
       <c r="R10" s="4" t="inlineStr"/>
       <c r="S10" s="4" t="inlineStr"/>
       <c r="T10" s="5" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11">
@@ -5109,7 +5332,9 @@
       <c r="H11" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="I11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="J11" s="5" t="n">
         <v>6</v>
       </c>
@@ -5135,7 +5360,7 @@
       <c r="R11" s="5" t="inlineStr"/>
       <c r="S11" s="5" t="inlineStr"/>
       <c r="T11" s="5" t="n">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
   </sheetData>

--- a/master_activity.xlsx
+++ b/master_activity.xlsx
@@ -19,6 +19,7 @@
     <sheet name="Wk 07-27-2026" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Wk 08-03-2026" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Wk 08-10-2026" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Wk 08-17-2026" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Weeks'!$A$1:$T$1</definedName>
@@ -531,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T74"/>
+  <dimension ref="A1:T65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3155,7 +3156,7 @@
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>08/17/2026 - 08/23/2026</t>
+          <t>08/10/2026 - 08/16/2026</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -3165,89 +3166,105 @@
       </c>
       <c r="C56" s="8" t="inlineStr"/>
       <c r="D56" s="8" t="inlineStr"/>
-      <c r="E56" s="8" t="inlineStr"/>
-      <c r="F56" s="8" t="inlineStr"/>
+      <c r="E56" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="G56" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H56" s="8" t="inlineStr"/>
+      <c r="I56" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J56" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K56" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="L56" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="M56" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="H56" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I56" s="8" t="inlineStr"/>
-      <c r="J56" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="L56" s="8" t="inlineStr"/>
-      <c r="M56" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="N56" s="8" t="inlineStr"/>
-      <c r="O56" s="8" t="inlineStr"/>
+      <c r="N56" s="8" t="n">
+        <v>218</v>
+      </c>
+      <c r="O56" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="P56" s="8" t="inlineStr"/>
       <c r="Q56" s="8" t="inlineStr"/>
       <c r="R56" s="8" t="inlineStr"/>
       <c r="S56" s="8" t="inlineStr"/>
       <c r="T56" s="5" t="n">
-        <v>34</v>
+        <v>281</v>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>08/17/2026 - 08/23/2026</t>
+          <t>08/10/2026 - 08/16/2026</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Michael Petrick</t>
+          <t>Christine Mello</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr"/>
-      <c r="D57" s="4" t="inlineStr"/>
-      <c r="E57" s="4" t="inlineStr"/>
+      <c r="D57" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="F57" s="4" t="inlineStr"/>
-      <c r="G57" s="4" t="inlineStr"/>
-      <c r="H57" s="4" t="inlineStr"/>
-      <c r="I57" s="4" t="inlineStr"/>
+      <c r="G57" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>4</v>
+      </c>
       <c r="J57" s="4" t="inlineStr"/>
       <c r="K57" s="4" t="inlineStr"/>
-      <c r="L57" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="L57" s="4" t="inlineStr"/>
       <c r="M57" s="4" t="inlineStr"/>
-      <c r="N57" s="4" t="n">
-        <v>289</v>
-      </c>
+      <c r="N57" s="4" t="inlineStr"/>
       <c r="O57" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P57" s="4" t="inlineStr"/>
       <c r="Q57" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R57" s="4" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="R57" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="S57" s="4" t="inlineStr"/>
       <c r="T57" s="5" t="n">
-        <v>294</v>
+        <v>34</v>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>08/17/2026 - 08/23/2026</t>
+          <t>08/10/2026 - 08/16/2026</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Roger Guzowski</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="n">
-        <v>191</v>
-      </c>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr"/>
       <c r="D58" s="8" t="inlineStr"/>
       <c r="E58" s="8" t="inlineStr"/>
       <c r="F58" s="8" t="inlineStr"/>
@@ -3256,8 +3273,12 @@
       <c r="I58" s="8" t="inlineStr"/>
       <c r="J58" s="8" t="inlineStr"/>
       <c r="K58" s="8" t="inlineStr"/>
-      <c r="L58" s="8" t="inlineStr"/>
-      <c r="M58" s="8" t="inlineStr"/>
+      <c r="L58" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M58" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="N58" s="8" t="inlineStr"/>
       <c r="O58" s="8" t="inlineStr"/>
       <c r="P58" s="8" t="inlineStr"/>
@@ -3265,726 +3286,351 @@
       <c r="R58" s="8" t="inlineStr"/>
       <c r="S58" s="8" t="inlineStr"/>
       <c r="T58" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>08/10/2026 - 08/16/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr"/>
+      <c r="D59" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
+      <c r="G59" s="4" t="inlineStr"/>
+      <c r="H59" s="4" t="inlineStr"/>
+      <c r="I59" s="4" t="inlineStr"/>
+      <c r="J59" s="4" t="inlineStr"/>
+      <c r="K59" s="4" t="inlineStr"/>
+      <c r="L59" s="4" t="inlineStr"/>
+      <c r="M59" s="4" t="inlineStr"/>
+      <c r="N59" s="4" t="inlineStr"/>
+      <c r="O59" s="4" t="inlineStr"/>
+      <c r="P59" s="4" t="inlineStr"/>
+      <c r="Q59" s="4" t="inlineStr"/>
+      <c r="R59" s="4" t="inlineStr"/>
+      <c r="S59" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T59" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 08/10/2026 - 08/16/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="5" t="inlineStr"/>
+      <c r="D60" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="M60" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="N60" s="5" t="n">
+        <v>218</v>
+      </c>
+      <c r="O60" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="P60" s="5" t="inlineStr"/>
+      <c r="Q60" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R60" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S60" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T60" s="5" t="n">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr"/>
+      <c r="D61" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="F61" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G61" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="H61" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I61" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J61" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="K61" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="L61" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="M61" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="N61" s="8" t="inlineStr"/>
+      <c r="O61" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="P61" s="8" t="inlineStr"/>
+      <c r="Q61" s="8" t="inlineStr"/>
+      <c r="R61" s="8" t="inlineStr"/>
+      <c r="S61" s="8" t="inlineStr"/>
+      <c r="T61" s="5" t="n">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr"/>
+      <c r="D62" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
+      <c r="H62" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr"/>
+      <c r="K62" s="4" t="inlineStr"/>
+      <c r="L62" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M62" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N62" s="4" t="inlineStr"/>
+      <c r="O62" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="P62" s="4" t="inlineStr"/>
+      <c r="Q62" s="4" t="inlineStr"/>
+      <c r="R62" s="4" t="inlineStr"/>
+      <c r="S62" s="4" t="inlineStr"/>
+      <c r="T62" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr"/>
+      <c r="D63" s="8" t="inlineStr"/>
+      <c r="E63" s="8" t="inlineStr"/>
+      <c r="F63" s="8" t="inlineStr"/>
+      <c r="G63" s="8" t="inlineStr"/>
+      <c r="H63" s="8" t="inlineStr"/>
+      <c r="I63" s="8" t="inlineStr"/>
+      <c r="J63" s="8" t="inlineStr"/>
+      <c r="K63" s="8" t="inlineStr"/>
+      <c r="L63" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M63" s="8" t="inlineStr"/>
+      <c r="N63" s="8" t="n">
+        <v>289</v>
+      </c>
+      <c r="O63" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P63" s="8" t="inlineStr"/>
+      <c r="Q63" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R63" s="8" t="inlineStr"/>
+      <c r="S63" s="8" t="inlineStr"/>
+      <c r="T63" s="5" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="n">
         <v>191</v>
       </c>
-    </row>
-    <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="9" t="inlineStr">
+      <c r="D64" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
+      <c r="G64" s="4" t="inlineStr"/>
+      <c r="H64" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr"/>
+      <c r="K64" s="4" t="inlineStr"/>
+      <c r="L64" s="4" t="inlineStr"/>
+      <c r="M64" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N64" s="4" t="inlineStr"/>
+      <c r="O64" s="4" t="inlineStr"/>
+      <c r="P64" s="4" t="inlineStr"/>
+      <c r="Q64" s="4" t="inlineStr"/>
+      <c r="R64" s="4" t="inlineStr"/>
+      <c r="S64" s="4" t="inlineStr"/>
+      <c r="T64" s="5" t="n">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="9" t="inlineStr">
         <is>
           <t>WEEK TOTAL — 08/17/2026 - 08/23/2026</t>
         </is>
       </c>
-      <c r="B59" s="10" t="n"/>
-      <c r="C59" s="5" t="n">
+      <c r="B65" s="10" t="n"/>
+      <c r="C65" s="5" t="n">
         <v>191</v>
       </c>
-      <c r="D59" s="5" t="inlineStr"/>
-      <c r="E59" s="5" t="inlineStr"/>
-      <c r="F59" s="5" t="inlineStr"/>
-      <c r="G59" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="H59" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K59" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="L59" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M59" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="N59" s="5" t="n">
+      <c r="D65" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J65" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="M65" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="N65" s="5" t="n">
         <v>289</v>
       </c>
-      <c r="O59" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="P59" s="5" t="inlineStr"/>
-      <c r="Q59" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R59" s="5" t="inlineStr"/>
-      <c r="S59" s="5" t="inlineStr"/>
-      <c r="T59" s="5" t="n">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>08/17/2026 - 08/23/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>Carlos Casillas</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="inlineStr"/>
-      <c r="D60" s="8" t="inlineStr"/>
-      <c r="E60" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F60" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G60" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="H60" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I60" s="8" t="inlineStr"/>
-      <c r="J60" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="K60" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="L60" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M60" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="N60" s="8" t="inlineStr"/>
-      <c r="O60" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="P60" s="8" t="inlineStr"/>
-      <c r="Q60" s="8" t="inlineStr"/>
-      <c r="R60" s="8" t="inlineStr"/>
-      <c r="S60" s="8" t="inlineStr"/>
-      <c r="T60" s="5" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>08/17/2026 - 08/23/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>Christine Mello</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr"/>
-      <c r="D61" s="4" t="inlineStr"/>
-      <c r="E61" s="4" t="inlineStr"/>
-      <c r="F61" s="4" t="inlineStr"/>
-      <c r="G61" s="4" t="inlineStr"/>
-      <c r="H61" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I61" s="4" t="inlineStr"/>
-      <c r="J61" s="4" t="inlineStr"/>
-      <c r="K61" s="4" t="inlineStr"/>
-      <c r="L61" s="4" t="inlineStr"/>
-      <c r="M61" s="4" t="inlineStr"/>
-      <c r="N61" s="4" t="inlineStr"/>
-      <c r="O61" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="P61" s="4" t="inlineStr"/>
-      <c r="Q61" s="4" t="inlineStr"/>
-      <c r="R61" s="4" t="inlineStr"/>
-      <c r="S61" s="4" t="inlineStr"/>
-      <c r="T61" s="5" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>08/17/2026 - 08/23/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>Michael Petrick</t>
-        </is>
-      </c>
-      <c r="C62" s="8" t="inlineStr"/>
-      <c r="D62" s="8" t="inlineStr"/>
-      <c r="E62" s="8" t="inlineStr"/>
-      <c r="F62" s="8" t="inlineStr"/>
-      <c r="G62" s="8" t="inlineStr"/>
-      <c r="H62" s="8" t="inlineStr"/>
-      <c r="I62" s="8" t="inlineStr"/>
-      <c r="J62" s="8" t="inlineStr"/>
-      <c r="K62" s="8" t="inlineStr"/>
-      <c r="L62" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M62" s="8" t="inlineStr"/>
-      <c r="N62" s="8" t="n">
-        <v>289</v>
-      </c>
-      <c r="O62" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="P62" s="8" t="inlineStr"/>
-      <c r="Q62" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R62" s="8" t="inlineStr"/>
-      <c r="S62" s="8" t="inlineStr"/>
-      <c r="T62" s="5" t="n">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>08/17/2026 - 08/23/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>Roger Guzowski</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="n">
-        <v>191</v>
-      </c>
-      <c r="D63" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E63" s="4" t="inlineStr"/>
-      <c r="F63" s="4" t="inlineStr"/>
-      <c r="G63" s="4" t="inlineStr"/>
-      <c r="H63" s="4" t="inlineStr"/>
-      <c r="I63" s="4" t="inlineStr"/>
-      <c r="J63" s="4" t="inlineStr"/>
-      <c r="K63" s="4" t="inlineStr"/>
-      <c r="L63" s="4" t="inlineStr"/>
-      <c r="M63" s="4" t="inlineStr"/>
-      <c r="N63" s="4" t="inlineStr"/>
-      <c r="O63" s="4" t="inlineStr"/>
-      <c r="P63" s="4" t="inlineStr"/>
-      <c r="Q63" s="4" t="inlineStr"/>
-      <c r="R63" s="4" t="inlineStr"/>
-      <c r="S63" s="4" t="inlineStr"/>
-      <c r="T63" s="5" t="n">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="9" t="inlineStr">
-        <is>
-          <t>WEEK TOTAL — 08/17/2026 - 08/23/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="10" t="n"/>
-      <c r="C64" s="5" t="n">
-        <v>191</v>
-      </c>
-      <c r="D64" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E64" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F64" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="H64" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I64" s="5" t="inlineStr"/>
-      <c r="J64" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K64" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M64" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="N64" s="5" t="n">
-        <v>289</v>
-      </c>
-      <c r="O64" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="P64" s="5" t="inlineStr"/>
-      <c r="Q64" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R64" s="5" t="inlineStr"/>
-      <c r="S64" s="5" t="inlineStr"/>
-      <c r="T64" s="5" t="n">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>08/10/2026 - 08/16/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>Carlos Casillas</t>
-        </is>
-      </c>
-      <c r="C65" s="8" t="inlineStr"/>
-      <c r="D65" s="8" t="inlineStr"/>
-      <c r="E65" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F65" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G65" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="H65" s="8" t="inlineStr"/>
-      <c r="I65" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="J65" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K65" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="L65" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="M65" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="N65" s="8" t="n">
-        <v>218</v>
-      </c>
-      <c r="O65" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="P65" s="8" t="inlineStr"/>
-      <c r="Q65" s="8" t="inlineStr"/>
-      <c r="R65" s="8" t="inlineStr"/>
-      <c r="S65" s="8" t="inlineStr"/>
+      <c r="O65" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="P65" s="5" t="inlineStr"/>
+      <c r="Q65" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R65" s="5" t="inlineStr"/>
+      <c r="S65" s="5" t="inlineStr"/>
       <c r="T65" s="5" t="n">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>08/10/2026 - 08/16/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>Christine Mello</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr"/>
-      <c r="D66" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E66" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F66" s="4" t="inlineStr"/>
-      <c r="G66" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H66" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="I66" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr"/>
-      <c r="K66" s="4" t="inlineStr"/>
-      <c r="L66" s="4" t="inlineStr"/>
-      <c r="M66" s="4" t="inlineStr"/>
-      <c r="N66" s="4" t="inlineStr"/>
-      <c r="O66" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="P66" s="4" t="inlineStr"/>
-      <c r="Q66" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R66" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="S66" s="4" t="inlineStr"/>
-      <c r="T66" s="5" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>08/10/2026 - 08/16/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>Michael Petrick</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="inlineStr"/>
-      <c r="D67" s="8" t="inlineStr"/>
-      <c r="E67" s="8" t="inlineStr"/>
-      <c r="F67" s="8" t="inlineStr"/>
-      <c r="G67" s="8" t="inlineStr"/>
-      <c r="H67" s="8" t="inlineStr"/>
-      <c r="I67" s="8" t="inlineStr"/>
-      <c r="J67" s="8" t="inlineStr"/>
-      <c r="K67" s="8" t="inlineStr"/>
-      <c r="L67" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M67" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N67" s="8" t="inlineStr"/>
-      <c r="O67" s="8" t="inlineStr"/>
-      <c r="P67" s="8" t="inlineStr"/>
-      <c r="Q67" s="8" t="inlineStr"/>
-      <c r="R67" s="8" t="inlineStr"/>
-      <c r="S67" s="8" t="inlineStr"/>
-      <c r="T67" s="5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="68" ht="22" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>08/10/2026 - 08/16/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>Roger Guzowski</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr"/>
-      <c r="D68" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E68" s="4" t="inlineStr"/>
-      <c r="F68" s="4" t="inlineStr"/>
-      <c r="G68" s="4" t="inlineStr"/>
-      <c r="H68" s="4" t="inlineStr"/>
-      <c r="I68" s="4" t="inlineStr"/>
-      <c r="J68" s="4" t="inlineStr"/>
-      <c r="K68" s="4" t="inlineStr"/>
-      <c r="L68" s="4" t="inlineStr"/>
-      <c r="M68" s="4" t="inlineStr"/>
-      <c r="N68" s="4" t="inlineStr"/>
-      <c r="O68" s="4" t="inlineStr"/>
-      <c r="P68" s="4" t="inlineStr"/>
-      <c r="Q68" s="4" t="inlineStr"/>
-      <c r="R68" s="4" t="inlineStr"/>
-      <c r="S68" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="T68" s="5" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="9" t="inlineStr">
-        <is>
-          <t>WEEK TOTAL — 08/10/2026 - 08/16/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="10" t="n"/>
-      <c r="C69" s="5" t="inlineStr"/>
-      <c r="D69" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="E69" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F69" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G69" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="H69" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="I69" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="J69" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K69" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="L69" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="M69" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="N69" s="5" t="n">
-        <v>218</v>
-      </c>
-      <c r="O69" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="P69" s="5" t="inlineStr"/>
-      <c r="Q69" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="R69" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S69" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T69" s="5" t="n">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>08/17/2026 - 08/23/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>Carlos Casillas</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr"/>
-      <c r="D70" s="4" t="inlineStr"/>
-      <c r="E70" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="F70" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G70" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="H70" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I70" s="4" t="inlineStr"/>
-      <c r="J70" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K70" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="L70" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M70" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="N70" s="4" t="inlineStr"/>
-      <c r="O70" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="P70" s="4" t="inlineStr"/>
-      <c r="Q70" s="4" t="inlineStr"/>
-      <c r="R70" s="4" t="inlineStr"/>
-      <c r="S70" s="4" t="inlineStr"/>
-      <c r="T70" s="5" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="71" ht="22" customHeight="1">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>08/17/2026 - 08/23/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>Christine Mello</t>
-        </is>
-      </c>
-      <c r="C71" s="8" t="inlineStr"/>
-      <c r="D71" s="8" t="inlineStr"/>
-      <c r="E71" s="8" t="inlineStr"/>
-      <c r="F71" s="8" t="inlineStr"/>
-      <c r="G71" s="8" t="inlineStr"/>
-      <c r="H71" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="I71" s="8" t="inlineStr"/>
-      <c r="J71" s="8" t="inlineStr"/>
-      <c r="K71" s="8" t="inlineStr"/>
-      <c r="L71" s="8" t="inlineStr"/>
-      <c r="M71" s="8" t="inlineStr"/>
-      <c r="N71" s="8" t="inlineStr"/>
-      <c r="O71" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="P71" s="8" t="inlineStr"/>
-      <c r="Q71" s="8" t="inlineStr"/>
-      <c r="R71" s="8" t="inlineStr"/>
-      <c r="S71" s="8" t="inlineStr"/>
-      <c r="T71" s="5" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="72" ht="22" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>08/17/2026 - 08/23/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>Michael Petrick</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr"/>
-      <c r="D72" s="4" t="inlineStr"/>
-      <c r="E72" s="4" t="inlineStr"/>
-      <c r="F72" s="4" t="inlineStr"/>
-      <c r="G72" s="4" t="inlineStr"/>
-      <c r="H72" s="4" t="inlineStr"/>
-      <c r="I72" s="4" t="inlineStr"/>
-      <c r="J72" s="4" t="inlineStr"/>
-      <c r="K72" s="4" t="inlineStr"/>
-      <c r="L72" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M72" s="4" t="inlineStr"/>
-      <c r="N72" s="4" t="n">
-        <v>289</v>
-      </c>
-      <c r="O72" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="P72" s="4" t="inlineStr"/>
-      <c r="Q72" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R72" s="4" t="inlineStr"/>
-      <c r="S72" s="4" t="inlineStr"/>
-      <c r="T72" s="5" t="n">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="73" ht="22" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>08/17/2026 - 08/23/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>Roger Guzowski</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="n">
-        <v>191</v>
-      </c>
-      <c r="D73" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E73" s="8" t="inlineStr"/>
-      <c r="F73" s="8" t="inlineStr"/>
-      <c r="G73" s="8" t="inlineStr"/>
-      <c r="H73" s="8" t="inlineStr"/>
-      <c r="I73" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" s="8" t="inlineStr"/>
-      <c r="K73" s="8" t="inlineStr"/>
-      <c r="L73" s="8" t="inlineStr"/>
-      <c r="M73" s="8" t="inlineStr"/>
-      <c r="N73" s="8" t="inlineStr"/>
-      <c r="O73" s="8" t="inlineStr"/>
-      <c r="P73" s="8" t="inlineStr"/>
-      <c r="Q73" s="8" t="inlineStr"/>
-      <c r="R73" s="8" t="inlineStr"/>
-      <c r="S73" s="8" t="inlineStr"/>
-      <c r="T73" s="5" t="n">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="74" ht="22" customHeight="1">
-      <c r="A74" s="9" t="inlineStr">
-        <is>
-          <t>WEEK TOTAL — 08/17/2026 - 08/23/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="10" t="n"/>
-      <c r="C74" s="5" t="n">
-        <v>191</v>
-      </c>
-      <c r="D74" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E74" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F74" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G74" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="H74" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I74" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J74" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K74" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="L74" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="M74" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="N74" s="5" t="n">
-        <v>289</v>
-      </c>
-      <c r="O74" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="P74" s="5" t="inlineStr"/>
-      <c r="Q74" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R74" s="5" t="inlineStr"/>
-      <c r="S74" s="5" t="inlineStr"/>
-      <c r="T74" s="5" t="n">
-        <v>566</v>
-      </c>
-    </row>
+        <v>720</v>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1"/>
+    <row r="67" ht="22" customHeight="1"/>
+    <row r="68" ht="22" customHeight="1"/>
+    <row r="69" ht="22" customHeight="1"/>
+    <row r="70" ht="22" customHeight="1"/>
+    <row r="71" ht="22" customHeight="1"/>
+    <row r="72" ht="22" customHeight="1"/>
+    <row r="73" ht="22" customHeight="1"/>
+    <row r="74" ht="22" customHeight="1"/>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A15:B15"/>
@@ -3994,6 +3640,7 @@
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A69:B69"/>
     <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A65:B65"/>
     <mergeCell ref="A74:B74"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A27:B27"/>
@@ -5372,6 +5019,383 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Activity/General Notes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Completed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Scheduled</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Via Email</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Successful</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Unsuccessful</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call via Phone</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Phone Call</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Site Visit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Group Email</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Payment Delivery</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Incoming</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Outgoing</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="N2" s="4" t="inlineStr"/>
+      <c r="O2" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="P2" s="4" t="inlineStr"/>
+      <c r="Q2" s="4" t="inlineStr"/>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
+      <c r="T2" s="5" t="n">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr"/>
+      <c r="H3" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P3" s="8" t="inlineStr"/>
+      <c r="Q3" s="8" t="inlineStr"/>
+      <c r="R3" s="8" t="inlineStr"/>
+      <c r="S3" s="8" t="inlineStr"/>
+      <c r="T3" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="n">
+        <v>289</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="5" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>191</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="8" t="inlineStr"/>
+      <c r="M5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="inlineStr"/>
+      <c r="T5" s="5" t="n">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="5" t="n">
+        <v>191</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>289</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="n">
+        <v>720</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:B6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/master_activity.xlsx
+++ b/master_activity.xlsx
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T65"/>
+  <dimension ref="A1:T77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3383,259 +3383,400 @@
         <v>329</v>
       </c>
     </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>08/17/2026 - 08/23/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>Carlos Casillas</t>
-        </is>
-      </c>
-      <c r="C61" s="8" t="inlineStr"/>
-      <c r="D61" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="F61" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="G61" s="8" t="n">
-        <v>31</v>
-      </c>
-      <c r="H61" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I61" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J61" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="K61" s="8" t="n">
-        <v>43</v>
-      </c>
-      <c r="L61" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="M61" s="8" t="n">
-        <v>38</v>
-      </c>
-      <c r="N61" s="8" t="inlineStr"/>
-      <c r="O61" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="P61" s="8" t="inlineStr"/>
-      <c r="Q61" s="8" t="inlineStr"/>
-      <c r="R61" s="8" t="inlineStr"/>
-      <c r="S61" s="8" t="inlineStr"/>
-      <c r="T61" s="5" t="n">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>08/17/2026 - 08/23/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>Christine Mello</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr"/>
-      <c r="D62" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" s="4" t="inlineStr"/>
-      <c r="F62" s="4" t="inlineStr"/>
-      <c r="G62" s="4" t="inlineStr"/>
-      <c r="H62" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I62" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr"/>
-      <c r="K62" s="4" t="inlineStr"/>
-      <c r="L62" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M62" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N62" s="4" t="inlineStr"/>
-      <c r="O62" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="P62" s="4" t="inlineStr"/>
-      <c r="Q62" s="4" t="inlineStr"/>
-      <c r="R62" s="4" t="inlineStr"/>
-      <c r="S62" s="4" t="inlineStr"/>
-      <c r="T62" s="5" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>08/17/2026 - 08/23/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>Michael Petrick</t>
-        </is>
-      </c>
-      <c r="C63" s="8" t="inlineStr"/>
-      <c r="D63" s="8" t="inlineStr"/>
-      <c r="E63" s="8" t="inlineStr"/>
-      <c r="F63" s="8" t="inlineStr"/>
-      <c r="G63" s="8" t="inlineStr"/>
-      <c r="H63" s="8" t="inlineStr"/>
-      <c r="I63" s="8" t="inlineStr"/>
-      <c r="J63" s="8" t="inlineStr"/>
-      <c r="K63" s="8" t="inlineStr"/>
-      <c r="L63" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M63" s="8" t="inlineStr"/>
-      <c r="N63" s="8" t="n">
-        <v>289</v>
-      </c>
-      <c r="O63" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="P63" s="8" t="inlineStr"/>
-      <c r="Q63" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R63" s="8" t="inlineStr"/>
-      <c r="S63" s="8" t="inlineStr"/>
-      <c r="T63" s="5" t="n">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>08/17/2026 - 08/23/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>Roger Guzowski</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="n">
-        <v>191</v>
-      </c>
-      <c r="D64" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E64" s="4" t="inlineStr"/>
-      <c r="F64" s="4" t="inlineStr"/>
-      <c r="G64" s="4" t="inlineStr"/>
-      <c r="H64" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I64" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr"/>
-      <c r="K64" s="4" t="inlineStr"/>
-      <c r="L64" s="4" t="inlineStr"/>
-      <c r="M64" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="N64" s="4" t="inlineStr"/>
-      <c r="O64" s="4" t="inlineStr"/>
-      <c r="P64" s="4" t="inlineStr"/>
-      <c r="Q64" s="4" t="inlineStr"/>
-      <c r="R64" s="4" t="inlineStr"/>
-      <c r="S64" s="4" t="inlineStr"/>
-      <c r="T64" s="5" t="n">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="9" t="inlineStr">
-        <is>
-          <t>WEEK TOTAL — 08/17/2026 - 08/23/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="10" t="n"/>
-      <c r="C65" s="5" t="n">
-        <v>191</v>
-      </c>
-      <c r="D65" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="E65" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="F65" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="H65" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="I65" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J65" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="K65" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="L65" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="M65" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="N65" s="5" t="n">
-        <v>289</v>
-      </c>
-      <c r="O65" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="P65" s="5" t="inlineStr"/>
-      <c r="Q65" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R65" s="5" t="inlineStr"/>
-      <c r="S65" s="5" t="inlineStr"/>
-      <c r="T65" s="5" t="n">
-        <v>720</v>
-      </c>
-    </row>
+    <row r="61" ht="22" customHeight="1"/>
+    <row r="62" ht="22" customHeight="1"/>
+    <row r="63" ht="22" customHeight="1"/>
+    <row r="64" ht="22" customHeight="1"/>
+    <row r="65" ht="22" customHeight="1"/>
     <row r="66" ht="22" customHeight="1"/>
     <row r="67" ht="22" customHeight="1"/>
     <row r="68" ht="22" customHeight="1"/>
     <row r="69" ht="22" customHeight="1"/>
-    <row r="70" ht="22" customHeight="1"/>
-    <row r="71" ht="22" customHeight="1"/>
-    <row r="72" ht="22" customHeight="1"/>
-    <row r="73" ht="22" customHeight="1"/>
-    <row r="74" ht="22" customHeight="1"/>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr"/>
+      <c r="D70" s="4" t="inlineStr"/>
+      <c r="E70" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I70" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J70" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K70" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="L70" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M70" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="N70" s="4" t="inlineStr"/>
+      <c r="O70" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="P70" s="4" t="inlineStr"/>
+      <c r="Q70" s="4" t="inlineStr"/>
+      <c r="R70" s="4" t="inlineStr"/>
+      <c r="S70" s="4" t="inlineStr"/>
+      <c r="T70" s="5" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr"/>
+      <c r="D71" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="8" t="inlineStr"/>
+      <c r="F71" s="8" t="inlineStr"/>
+      <c r="G71" s="8" t="inlineStr"/>
+      <c r="H71" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I71" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" s="8" t="inlineStr"/>
+      <c r="K71" s="8" t="inlineStr"/>
+      <c r="L71" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M71" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N71" s="8" t="inlineStr"/>
+      <c r="O71" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P71" s="8" t="inlineStr"/>
+      <c r="Q71" s="8" t="inlineStr"/>
+      <c r="R71" s="8" t="inlineStr"/>
+      <c r="S71" s="8" t="inlineStr"/>
+      <c r="T71" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr"/>
+      <c r="D72" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr"/>
+      <c r="H72" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I72" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr"/>
+      <c r="K72" s="4" t="inlineStr"/>
+      <c r="L72" s="4" t="inlineStr"/>
+      <c r="M72" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N72" s="4" t="inlineStr"/>
+      <c r="O72" s="4" t="inlineStr"/>
+      <c r="P72" s="4" t="inlineStr"/>
+      <c r="Q72" s="4" t="inlineStr"/>
+      <c r="R72" s="4" t="inlineStr"/>
+      <c r="S72" s="4" t="inlineStr"/>
+      <c r="T72" s="5" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="n"/>
+      <c r="C73" s="5" t="inlineStr"/>
+      <c r="D73" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M73" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="N73" s="5" t="inlineStr"/>
+      <c r="O73" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="P73" s="5" t="inlineStr"/>
+      <c r="Q73" s="5" t="inlineStr"/>
+      <c r="R73" s="5" t="inlineStr"/>
+      <c r="S73" s="5" t="inlineStr"/>
+      <c r="T73" s="5" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>08/24/2026 - 08/30/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr"/>
+      <c r="D74" s="4" t="inlineStr"/>
+      <c r="E74" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H74" s="4" t="inlineStr"/>
+      <c r="I74" s="4" t="inlineStr"/>
+      <c r="J74" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K74" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L74" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M74" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N74" s="4" t="inlineStr"/>
+      <c r="O74" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P74" s="4" t="inlineStr"/>
+      <c r="Q74" s="4" t="inlineStr"/>
+      <c r="R74" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S74" s="4" t="inlineStr"/>
+      <c r="T74" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>08/24/2026 - 08/30/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr"/>
+      <c r="D75" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E75" s="8" t="inlineStr"/>
+      <c r="F75" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H75" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I75" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J75" s="8" t="inlineStr"/>
+      <c r="K75" s="8" t="inlineStr"/>
+      <c r="L75" s="8" t="inlineStr"/>
+      <c r="M75" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="N75" s="8" t="inlineStr"/>
+      <c r="O75" s="8" t="inlineStr"/>
+      <c r="P75" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" s="8" t="inlineStr"/>
+      <c r="R75" s="8" t="inlineStr"/>
+      <c r="S75" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T75" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>08/24/2026 - 08/30/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr"/>
+      <c r="D76" s="4" t="inlineStr"/>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G76" s="4" t="inlineStr"/>
+      <c r="H76" s="4" t="inlineStr"/>
+      <c r="I76" s="4" t="inlineStr"/>
+      <c r="J76" s="4" t="inlineStr"/>
+      <c r="K76" s="4" t="inlineStr"/>
+      <c r="L76" s="4" t="inlineStr"/>
+      <c r="M76" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N76" s="4" t="inlineStr"/>
+      <c r="O76" s="4" t="inlineStr"/>
+      <c r="P76" s="4" t="inlineStr"/>
+      <c r="Q76" s="4" t="inlineStr"/>
+      <c r="R76" s="4" t="inlineStr"/>
+      <c r="S76" s="4" t="inlineStr"/>
+      <c r="T76" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 08/24/2026 - 08/30/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="10" t="n"/>
+      <c r="C77" s="5" t="inlineStr"/>
+      <c r="D77" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M77" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="N77" s="5" t="inlineStr"/>
+      <c r="O77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q77" s="5" t="inlineStr"/>
+      <c r="R77" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="S77" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T77" s="5" t="n">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <mergeCells count="21">
+  <mergeCells count="23">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A64:B64"/>
     <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A73:B73"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A69:B69"/>
@@ -3647,6 +3788,7 @@
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A77:B77"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A10:B10"/>
@@ -5025,7 +5167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5164,9 +5306,7 @@
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr"/>
-      <c r="D2" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="D2" s="4" t="inlineStr"/>
       <c r="E2" s="4" t="n">
         <v>17</v>
       </c>
@@ -5203,7 +5343,7 @@
       <c r="R2" s="4" t="inlineStr"/>
       <c r="S2" s="4" t="inlineStr"/>
       <c r="T2" s="5" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -5258,139 +5398,282 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Michael Petrick</t>
+          <t>Roger Guzowski</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="n">
+        <v>7</v>
+      </c>
       <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="J4" s="4" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="n">
-        <v>289</v>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr"/>
       <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q4" s="4" t="inlineStr"/>
       <c r="R4" s="4" t="inlineStr"/>
       <c r="S4" s="4" t="inlineStr"/>
       <c r="T4" s="5" t="n">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>08/17/2026 - 08/23/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 08/17/2026 - 08/23/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="N5" s="5" t="inlineStr"/>
+      <c r="O5" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="P5" s="5" t="inlineStr"/>
+      <c r="Q5" s="5" t="inlineStr"/>
+      <c r="R5" s="5" t="inlineStr"/>
+      <c r="S5" s="5" t="inlineStr"/>
+      <c r="T5" s="5" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>08/24/2026 - 08/30/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" s="4" t="inlineStr"/>
+      <c r="O6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>08/24/2026 - 08/30/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr"/>
+      <c r="D7" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" s="8" t="inlineStr"/>
+      <c r="F7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" s="8" t="inlineStr"/>
+      <c r="K7" s="8" t="inlineStr"/>
+      <c r="L7" s="8" t="inlineStr"/>
+      <c r="M7" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="N7" s="8" t="inlineStr"/>
+      <c r="O7" s="8" t="inlineStr"/>
+      <c r="P7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="8" t="inlineStr"/>
+      <c r="R7" s="8" t="inlineStr"/>
+      <c r="S7" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>08/24/2026 - 08/30/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Roger Guzowski</t>
         </is>
       </c>
-      <c r="C5" s="8" t="n">
-        <v>191</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="n">
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr"/>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr"/>
+      <c r="T8" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 08/24/2026 - 08/30/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="I5" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" s="8" t="inlineStr"/>
-      <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="8" t="inlineStr"/>
-      <c r="M5" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" s="8" t="inlineStr"/>
-      <c r="O5" s="8" t="inlineStr"/>
-      <c r="P5" s="8" t="inlineStr"/>
-      <c r="Q5" s="8" t="inlineStr"/>
-      <c r="R5" s="8" t="inlineStr"/>
-      <c r="S5" s="8" t="inlineStr"/>
-      <c r="T5" s="5" t="n">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>WEEK TOTAL — 08/17/2026 - 08/23/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="n"/>
-      <c r="C6" s="5" t="n">
-        <v>191</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v>289</v>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" s="5" t="inlineStr"/>
-      <c r="S6" s="5" t="inlineStr"/>
-      <c r="T6" s="5" t="n">
-        <v>720</v>
+      <c r="L9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="S9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" s="5" t="n">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:B6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/master_activity.xlsx
+++ b/master_activity.xlsx
@@ -20,6 +20,7 @@
     <sheet name="Wk 08-03-2026" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Wk 08-10-2026" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Wk 08-17-2026" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Wk 08-24-2026" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Weeks'!$A$1:$T$1</definedName>
@@ -532,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T77"/>
+  <dimension ref="A1:T82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3592,31 +3593,33 @@
       <c r="C74" s="4" t="inlineStr"/>
       <c r="D74" s="4" t="inlineStr"/>
       <c r="E74" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
-      <c r="I74" s="4" t="inlineStr"/>
+      <c r="I74" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="J74" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="N74" s="4" t="inlineStr"/>
       <c r="O74" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P74" s="4" t="inlineStr"/>
       <c r="Q74" s="4" t="inlineStr"/>
@@ -3625,7 +3628,7 @@
       </c>
       <c r="S74" s="4" t="inlineStr"/>
       <c r="T74" s="5" t="n">
-        <v>21</v>
+        <v>93</v>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
@@ -3641,26 +3644,26 @@
       </c>
       <c r="C75" s="8" t="inlineStr"/>
       <c r="D75" s="8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E75" s="8" t="inlineStr"/>
       <c r="F75" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G75" s="8" t="n">
         <v>8</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I75" s="8" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J75" s="8" t="inlineStr"/>
       <c r="K75" s="8" t="inlineStr"/>
       <c r="L75" s="8" t="inlineStr"/>
       <c r="M75" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N75" s="8" t="inlineStr"/>
       <c r="O75" s="8" t="inlineStr"/>
@@ -3668,12 +3671,14 @@
         <v>1</v>
       </c>
       <c r="Q75" s="8" t="inlineStr"/>
-      <c r="R75" s="8" t="inlineStr"/>
+      <c r="R75" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="S75" s="8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T75" s="5" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1">
@@ -3684,102 +3689,314 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Roger Guzowski</t>
+          <t>Michael Petrick</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr"/>
       <c r="D76" s="4" t="inlineStr"/>
       <c r="E76" s="4" t="inlineStr"/>
-      <c r="F76" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="F76" s="4" t="inlineStr"/>
       <c r="G76" s="4" t="inlineStr"/>
       <c r="H76" s="4" t="inlineStr"/>
       <c r="I76" s="4" t="inlineStr"/>
       <c r="J76" s="4" t="inlineStr"/>
       <c r="K76" s="4" t="inlineStr"/>
       <c r="L76" s="4" t="inlineStr"/>
-      <c r="M76" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="M76" s="4" t="inlineStr"/>
       <c r="N76" s="4" t="inlineStr"/>
-      <c r="O76" s="4" t="inlineStr"/>
+      <c r="O76" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="P76" s="4" t="inlineStr"/>
       <c r="Q76" s="4" t="inlineStr"/>
       <c r="R76" s="4" t="inlineStr"/>
       <c r="S76" s="4" t="inlineStr"/>
       <c r="T76" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>08/24/2026 - 08/30/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr"/>
+      <c r="D77" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="8" t="inlineStr"/>
+      <c r="F77" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G77" s="8" t="inlineStr"/>
+      <c r="H77" s="8" t="inlineStr"/>
+      <c r="I77" s="8" t="inlineStr"/>
+      <c r="J77" s="8" t="inlineStr"/>
+      <c r="K77" s="8" t="inlineStr"/>
+      <c r="L77" s="8" t="inlineStr"/>
+      <c r="M77" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N77" s="8" t="inlineStr"/>
+      <c r="O77" s="8" t="inlineStr"/>
+      <c r="P77" s="8" t="inlineStr"/>
+      <c r="Q77" s="8" t="inlineStr"/>
+      <c r="R77" s="8" t="inlineStr"/>
+      <c r="S77" s="8" t="inlineStr"/>
+      <c r="T77" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 08/24/2026 - 08/30/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="10" t="n"/>
+      <c r="C78" s="5" t="inlineStr"/>
+      <c r="D78" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="J78" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="L78" s="5" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="9" t="inlineStr">
-        <is>
-          <t>WEEK TOTAL — 08/24/2026 - 08/30/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="10" t="n"/>
-      <c r="C77" s="5" t="inlineStr"/>
-      <c r="D77" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E77" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F77" s="5" t="n">
+      <c r="M78" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="N78" s="5" t="inlineStr"/>
+      <c r="O78" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P78" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q78" s="5" t="inlineStr"/>
+      <c r="R78" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G77" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="H77" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I77" s="5" t="n">
+      <c r="S78" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="T78" s="5" t="n">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>08/31/2026 - 09/06/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr"/>
+      <c r="D79" s="8" t="inlineStr"/>
+      <c r="E79" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="J77" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K77" s="5" t="n">
+      <c r="F79" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G79" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H79" s="8" t="inlineStr"/>
+      <c r="I79" s="8" t="inlineStr"/>
+      <c r="J79" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="L77" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M77" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="N77" s="5" t="inlineStr"/>
-      <c r="O77" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P77" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q77" s="5" t="inlineStr"/>
-      <c r="R77" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="S77" s="5" t="n">
+      <c r="K79" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="L79" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="M79" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="N79" s="8" t="inlineStr"/>
+      <c r="O79" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P79" s="8" t="inlineStr"/>
+      <c r="Q79" s="8" t="inlineStr"/>
+      <c r="R79" s="8" t="inlineStr"/>
+      <c r="S79" s="8" t="inlineStr"/>
+      <c r="T79" s="5" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>08/31/2026 - 09/06/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr"/>
+      <c r="D80" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr"/>
+      <c r="G80" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H80" s="4" t="inlineStr"/>
+      <c r="I80" s="4" t="inlineStr"/>
+      <c r="J80" s="4" t="inlineStr"/>
+      <c r="K80" s="4" t="inlineStr"/>
+      <c r="L80" s="4" t="inlineStr"/>
+      <c r="M80" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N80" s="4" t="inlineStr"/>
+      <c r="O80" s="4" t="inlineStr"/>
+      <c r="P80" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q80" s="4" t="inlineStr"/>
+      <c r="R80" s="4" t="inlineStr"/>
+      <c r="S80" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T80" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>08/31/2026 - 09/06/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr"/>
+      <c r="D81" s="8" t="inlineStr"/>
+      <c r="E81" s="8" t="inlineStr"/>
+      <c r="F81" s="8" t="inlineStr"/>
+      <c r="G81" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="8" t="inlineStr"/>
+      <c r="I81" s="8" t="inlineStr"/>
+      <c r="J81" s="8" t="inlineStr"/>
+      <c r="K81" s="8" t="inlineStr"/>
+      <c r="L81" s="8" t="inlineStr"/>
+      <c r="M81" s="8" t="inlineStr"/>
+      <c r="N81" s="8" t="inlineStr"/>
+      <c r="O81" s="8" t="inlineStr"/>
+      <c r="P81" s="8" t="inlineStr"/>
+      <c r="Q81" s="8" t="inlineStr"/>
+      <c r="R81" s="8" t="inlineStr"/>
+      <c r="S81" s="8" t="inlineStr"/>
+      <c r="T81" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 08/31/2026 - 09/06/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="n"/>
+      <c r="C82" s="5" t="inlineStr"/>
+      <c r="D82" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E82" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="T77" s="5" t="n">
-        <v>59</v>
+      <c r="F82" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H82" s="5" t="inlineStr"/>
+      <c r="I82" s="5" t="inlineStr"/>
+      <c r="J82" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="M82" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="N82" s="5" t="inlineStr"/>
+      <c r="O82" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P82" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q82" s="5" t="inlineStr"/>
+      <c r="R82" s="5" t="inlineStr"/>
+      <c r="S82" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T82" s="5" t="n">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <mergeCells count="23">
+  <mergeCells count="25">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A82:B82"/>
     <mergeCell ref="A60:B60"/>
     <mergeCell ref="A73:B73"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A78:B78"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A65:B65"/>
     <mergeCell ref="A74:B74"/>
@@ -5679,6 +5896,552 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Activity/General Notes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Completed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Scheduled</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Via Email</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Successful</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Unsuccessful</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call via Phone</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Phone Call</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Site Visit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Group Email</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Payment Delivery</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Incoming</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Outgoing</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>08/24/2026 - 08/30/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="N2" s="4" t="inlineStr"/>
+      <c r="O2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P2" s="4" t="inlineStr"/>
+      <c r="Q2" s="4" t="inlineStr"/>
+      <c r="R2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S2" s="4" t="inlineStr"/>
+      <c r="T2" s="5" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>08/24/2026 - 08/30/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="8" t="inlineStr"/>
+      <c r="M3" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="inlineStr"/>
+      <c r="P3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="8" t="inlineStr"/>
+      <c r="R3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T3" s="5" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>08/24/2026 - 08/30/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>08/24/2026 - 08/30/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="8" t="inlineStr"/>
+      <c r="M5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="inlineStr"/>
+      <c r="T5" s="5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 08/24/2026 - 08/30/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>08/31/2026 - 09/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr"/>
+      <c r="D7" s="8" t="inlineStr"/>
+      <c r="E7" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" s="8" t="inlineStr"/>
+      <c r="I7" s="8" t="inlineStr"/>
+      <c r="J7" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="N7" s="8" t="inlineStr"/>
+      <c r="O7" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="8" t="inlineStr"/>
+      <c r="Q7" s="8" t="inlineStr"/>
+      <c r="R7" s="8" t="inlineStr"/>
+      <c r="S7" s="8" t="inlineStr"/>
+      <c r="T7" s="5" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>08/31/2026 - 09/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr"/>
+      <c r="P8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" s="5" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>08/31/2026 - 09/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr"/>
+      <c r="D9" s="8" t="inlineStr"/>
+      <c r="E9" s="8" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr"/>
+      <c r="G9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="8" t="inlineStr"/>
+      <c r="I9" s="8" t="inlineStr"/>
+      <c r="J9" s="8" t="inlineStr"/>
+      <c r="K9" s="8" t="inlineStr"/>
+      <c r="L9" s="8" t="inlineStr"/>
+      <c r="M9" s="8" t="inlineStr"/>
+      <c r="N9" s="8" t="inlineStr"/>
+      <c r="O9" s="8" t="inlineStr"/>
+      <c r="P9" s="8" t="inlineStr"/>
+      <c r="Q9" s="8" t="inlineStr"/>
+      <c r="R9" s="8" t="inlineStr"/>
+      <c r="S9" s="8" t="inlineStr"/>
+      <c r="T9" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 08/31/2026 - 09/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="5" t="inlineStr"/>
+      <c r="R10" s="5" t="inlineStr"/>
+      <c r="S10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" s="5" t="n">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A10:B10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/master_activity.xlsx
+++ b/master_activity.xlsx
@@ -21,6 +21,7 @@
     <sheet name="Wk 08-10-2026" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Wk 08-17-2026" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Wk 08-24-2026" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Wk 08-31-2026" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Weeks'!$A$1:$T$1</definedName>
@@ -533,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T82"/>
+  <dimension ref="A1:T83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3585,11 +3586,7 @@
           <t>08/24/2026 - 08/30/2026</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>Carlos Casillas</t>
-        </is>
-      </c>
+      <c r="B74" s="10" t="n"/>
       <c r="C74" s="4" t="inlineStr"/>
       <c r="D74" s="4" t="inlineStr"/>
       <c r="E74" s="4" t="n">
@@ -3721,11 +3718,7 @@
           <t>08/24/2026 - 08/30/2026</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>Roger Guzowski</t>
-        </is>
-      </c>
+      <c r="B77" s="10" t="n"/>
       <c r="C77" s="8" t="inlineStr"/>
       <c r="D77" s="8" t="n">
         <v>1</v>
@@ -3823,38 +3816,40 @@
       <c r="C79" s="8" t="inlineStr"/>
       <c r="D79" s="8" t="inlineStr"/>
       <c r="E79" s="8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F79" s="8" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G79" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="H79" s="8" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="H79" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="I79" s="8" t="inlineStr"/>
       <c r="J79" s="8" t="n">
         <v>5</v>
       </c>
       <c r="K79" s="8" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="L79" s="8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M79" s="8" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="N79" s="8" t="inlineStr"/>
       <c r="O79" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="P79" s="8" t="inlineStr"/>
       <c r="Q79" s="8" t="inlineStr"/>
       <c r="R79" s="8" t="inlineStr"/>
       <c r="S79" s="8" t="inlineStr"/>
       <c r="T79" s="5" t="n">
-        <v>69</v>
+        <v>139</v>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1">
@@ -3870,33 +3865,45 @@
       </c>
       <c r="C80" s="4" t="inlineStr"/>
       <c r="D80" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E80" s="4" t="inlineStr"/>
-      <c r="F80" s="4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="G80" s="4" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
       <c r="I80" s="4" t="inlineStr"/>
       <c r="J80" s="4" t="inlineStr"/>
       <c r="K80" s="4" t="inlineStr"/>
-      <c r="L80" s="4" t="inlineStr"/>
+      <c r="L80" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="M80" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N80" s="4" t="inlineStr"/>
-      <c r="O80" s="4" t="inlineStr"/>
+      <c r="O80" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="P80" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="Q80" s="4" t="inlineStr"/>
-      <c r="R80" s="4" t="inlineStr"/>
+      <c r="Q80" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R80" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="S80" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T80" s="5" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1">
@@ -3907,89 +3914,137 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Roger Guzowski</t>
+          <t>Michael Petrick</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr"/>
       <c r="D81" s="8" t="inlineStr"/>
       <c r="E81" s="8" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr"/>
-      <c r="G81" s="8" t="n">
-        <v>1</v>
-      </c>
+      <c r="G81" s="8" t="inlineStr"/>
       <c r="H81" s="8" t="inlineStr"/>
       <c r="I81" s="8" t="inlineStr"/>
       <c r="J81" s="8" t="inlineStr"/>
       <c r="K81" s="8" t="inlineStr"/>
-      <c r="L81" s="8" t="inlineStr"/>
+      <c r="L81" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="M81" s="8" t="inlineStr"/>
       <c r="N81" s="8" t="inlineStr"/>
-      <c r="O81" s="8" t="inlineStr"/>
+      <c r="O81" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="P81" s="8" t="inlineStr"/>
       <c r="Q81" s="8" t="inlineStr"/>
       <c r="R81" s="8" t="inlineStr"/>
       <c r="S81" s="8" t="inlineStr"/>
       <c r="T81" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1">
-      <c r="A82" s="9" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>08/31/2026 - 09/06/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="n">
+        <v>924</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr"/>
+      <c r="G82" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="4" t="inlineStr"/>
+      <c r="I82" s="4" t="inlineStr"/>
+      <c r="J82" s="4" t="inlineStr"/>
+      <c r="K82" s="4" t="inlineStr"/>
+      <c r="L82" s="4" t="inlineStr"/>
+      <c r="M82" s="4" t="inlineStr"/>
+      <c r="N82" s="4" t="inlineStr"/>
+      <c r="O82" s="4" t="inlineStr"/>
+      <c r="P82" s="4" t="inlineStr"/>
+      <c r="Q82" s="4" t="inlineStr"/>
+      <c r="R82" s="4" t="inlineStr"/>
+      <c r="S82" s="4" t="inlineStr"/>
+      <c r="T82" s="5" t="n">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="9" t="inlineStr">
         <is>
           <t>WEEK TOTAL — 08/31/2026 - 09/06/2026</t>
         </is>
       </c>
-      <c r="B82" s="10" t="n"/>
-      <c r="C82" s="5" t="inlineStr"/>
-      <c r="D82" s="5" t="n">
+      <c r="B83" s="10" t="n"/>
+      <c r="C83" s="5" t="n">
+        <v>924</v>
+      </c>
+      <c r="D83" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" s="5" t="inlineStr"/>
+      <c r="J83" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E82" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F82" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G82" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="H82" s="5" t="inlineStr"/>
-      <c r="I82" s="5" t="inlineStr"/>
-      <c r="J82" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="K82" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="L82" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="M82" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="N82" s="5" t="inlineStr"/>
-      <c r="O82" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="P82" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q82" s="5" t="inlineStr"/>
-      <c r="R82" s="5" t="inlineStr"/>
-      <c r="S82" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T82" s="5" t="n">
-        <v>87</v>
+      <c r="K83" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="M83" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="N83" s="5" t="inlineStr"/>
+      <c r="O83" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="P83" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q83" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R83" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S83" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T83" s="5" t="n">
+        <v>1118</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:T1"/>
-  <mergeCells count="25">
+  <mergeCells count="26">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A64:B64"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A64:B64"/>
     <mergeCell ref="A82:B82"/>
     <mergeCell ref="A60:B60"/>
     <mergeCell ref="A73:B73"/>
@@ -4009,6 +4064,7 @@
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A83:B83"/>
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A34:B34"/>
   </mergeCells>
@@ -6442,6 +6498,383 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Activity/General Notes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Completed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Appointment - Scheduled</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Via Email</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Successful</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call Visit - Unsuccessful</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Cold Call via Phone</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Phone Call</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Courtesy Site Visit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Group Email</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Payment Delivery</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Incoming</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Phone - Outgoing</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>08/31/2026 - 09/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Carlos Casillas</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr"/>
+      <c r="J2" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="L2" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="N2" s="4" t="inlineStr"/>
+      <c r="O2" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="P2" s="4" t="inlineStr"/>
+      <c r="Q2" s="4" t="inlineStr"/>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
+      <c r="T2" s="5" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>08/31/2026 - 09/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Christine Mello</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="H3" s="8" t="inlineStr"/>
+      <c r="I3" s="8" t="inlineStr"/>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" s="5" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>08/31/2026 - 09/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Michael Petrick</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>08/31/2026 - 09/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Roger Guzowski</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>924</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="8" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="inlineStr"/>
+      <c r="T5" s="5" t="n">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>WEEK TOTAL — 08/31/2026 - 09/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="5" t="n">
+        <v>924</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>1118</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:B6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
